--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
@@ -1528,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2146,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ5">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2352,10 +2352,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AQ6">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2764,10 +2764,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ8">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2970,10 +2970,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3176,19 +3176,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ10">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3376,25 +3376,25 @@
         <v>1.13</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ11">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3582,25 +3582,25 @@
         <v>2.1</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AU12">
         <v>9</v>
@@ -3788,25 +3788,25 @@
         <v>1.4</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP13">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -3994,25 +3994,25 @@
         <v>1.72</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ14">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4203,22 +4203,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ15">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4406,25 +4406,25 @@
         <v>1.3</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ16">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AU16">
         <v>7</v>
@@ -4612,25 +4612,25 @@
         <v>1.55</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ17">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4818,25 +4818,25 @@
         <v>1.8</v>
       </c>
       <c r="AN18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP18">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ18">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR18">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="AS18">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AT18">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AU18">
         <v>2</v>
@@ -5027,22 +5027,22 @@
         <v>1</v>
       </c>
       <c r="AO19">
+        <v>2</v>
+      </c>
+      <c r="AP19">
+        <v>1.76</v>
+      </c>
+      <c r="AQ19">
+        <v>1.14</v>
+      </c>
+      <c r="AR19">
+        <v>1.51</v>
+      </c>
+      <c r="AS19">
+        <v>1.49</v>
+      </c>
+      <c r="AT19">
         <v>3</v>
-      </c>
-      <c r="AP19">
-        <v>1.8</v>
-      </c>
-      <c r="AQ19">
-        <v>1.18</v>
-      </c>
-      <c r="AR19">
-        <v>1.85</v>
-      </c>
-      <c r="AS19">
-        <v>1.69</v>
-      </c>
-      <c r="AT19">
-        <v>3.54</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5230,25 +5230,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP20">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR20">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AS20">
-        <v>0.71</v>
+        <v>1.19</v>
       </c>
       <c r="AT20">
-        <v>2.16</v>
+        <v>2.83</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5439,22 +5439,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP21">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ21">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR21">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AS21">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AT21">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="AU21">
         <v>2</v>
@@ -5642,25 +5642,25 @@
         <v>2.35</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR22">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AS22">
-        <v>0.77</v>
+        <v>1.18</v>
       </c>
       <c r="AT22">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="AU22">
         <v>2</v>
@@ -5848,25 +5848,25 @@
         <v>1.95</v>
       </c>
       <c r="AN23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP23">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ23">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR23">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AS23">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AT23">
-        <v>4.23</v>
+        <v>3.77</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6054,25 +6054,25 @@
         <v>1.36</v>
       </c>
       <c r="AN24">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP24">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ24">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR24">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AS24">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="AT24">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AU24">
         <v>5</v>
@@ -6260,25 +6260,25 @@
         <v>1.26</v>
       </c>
       <c r="AN25">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO25">
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ25">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR25">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="AS25">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AT25">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6466,25 +6466,25 @@
         <v>1.63</v>
       </c>
       <c r="AN26">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ26">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR26">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AS26">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="AT26">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6672,25 +6672,25 @@
         <v>1.75</v>
       </c>
       <c r="AN27">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO27">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ27">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR27">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AS27">
-        <v>0.99</v>
+        <v>1.22</v>
       </c>
       <c r="AT27">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6878,25 +6878,25 @@
         <v>2.25</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP28">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR28">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AS28">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AT28">
-        <v>3.56</v>
+        <v>3.31</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7084,25 +7084,25 @@
         <v>2.35</v>
       </c>
       <c r="AN29">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP29">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR29">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="AS29">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="AT29">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AU29">
         <v>0</v>
@@ -7290,25 +7290,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AO30">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP30">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ30">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR30">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS30">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="AT30">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7496,25 +7496,25 @@
         <v>1.45</v>
       </c>
       <c r="AN31">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP31">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR31">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AS31">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AT31">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="AU31">
         <v>3</v>
@@ -7702,25 +7702,25 @@
         <v>1.72</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO32">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP32">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ32">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR32">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AS32">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AT32">
-        <v>3.44</v>
+        <v>3.16</v>
       </c>
       <c r="AU32">
         <v>5</v>
@@ -7908,25 +7908,25 @@
         <v>2</v>
       </c>
       <c r="AN33">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO33">
         <v>1</v>
       </c>
       <c r="AP33">
+        <v>1.76</v>
+      </c>
+      <c r="AQ33">
+        <v>1.14</v>
+      </c>
+      <c r="AR33">
         <v>1.8</v>
       </c>
-      <c r="AQ33">
-        <v>0.91</v>
-      </c>
-      <c r="AR33">
-        <v>2.11</v>
-      </c>
       <c r="AS33">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AT33">
-        <v>3.79</v>
+        <v>3.46</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8114,25 +8114,25 @@
         <v>1.68</v>
       </c>
       <c r="AN34">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO34">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ34">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR34">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AS34">
-        <v>0.9</v>
+        <v>1.13</v>
       </c>
       <c r="AT34">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8320,25 +8320,25 @@
         <v>1.47</v>
       </c>
       <c r="AN35">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AO35">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP35">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ35">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR35">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AS35">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AT35">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AU35">
         <v>8</v>
@@ -8526,25 +8526,25 @@
         <v>1.25</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ36">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR36">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AS36">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AT36">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8738,19 +8738,19 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ37">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR37">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AS37">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AT37">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8941,22 +8941,22 @@
         <v>1</v>
       </c>
       <c r="AO38">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AP38">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR38">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AS38">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="AT38">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AU38">
         <v>7</v>
@@ -9144,25 +9144,25 @@
         <v>1.34</v>
       </c>
       <c r="AN39">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AO39">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP39">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ39">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR39">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="AS39">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AT39">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9350,25 +9350,25 @@
         <v>1.44</v>
       </c>
       <c r="AN40">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO40">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP40">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ40">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR40">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AS40">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AT40">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9556,25 +9556,25 @@
         <v>1.57</v>
       </c>
       <c r="AN41">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO41">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP41">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ41">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR41">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AS41">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="AU41">
         <v>7</v>
@@ -9762,25 +9762,25 @@
         <v>2.35</v>
       </c>
       <c r="AN42">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AO42">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP42">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR42">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AS42">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT42">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="AU42">
         <v>12</v>
@@ -9968,25 +9968,25 @@
         <v>1.7</v>
       </c>
       <c r="AN43">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AO43">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP43">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR43">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AS43">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="AT43">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10174,25 +10174,25 @@
         <v>2.6</v>
       </c>
       <c r="AN44">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO44">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AP44">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR44">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="AS44">
         <v>1.49</v>
       </c>
       <c r="AT44">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="AU44">
         <v>3</v>
@@ -10380,25 +10380,25 @@
         <v>2</v>
       </c>
       <c r="AN45">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO45">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="AP45">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ45">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR45">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AS45">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AT45">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="AU45">
         <v>4</v>
@@ -10586,25 +10586,25 @@
         <v>1.62</v>
       </c>
       <c r="AN46">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO46">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ46">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR46">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AS46">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AT46">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10792,25 +10792,25 @@
         <v>2.02</v>
       </c>
       <c r="AN47">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ47">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR47">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS47">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="AT47">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10998,25 +10998,25 @@
         <v>1.45</v>
       </c>
       <c r="AN48">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO48">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AP48">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ48">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR48">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="AS48">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT48">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11204,25 +11204,25 @@
         <v>1.36</v>
       </c>
       <c r="AN49">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO49">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AP49">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ49">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR49">
+        <v>1.44</v>
+      </c>
+      <c r="AS49">
         <v>1.48</v>
       </c>
-      <c r="AS49">
-        <v>1.61</v>
-      </c>
       <c r="AT49">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11413,22 +11413,22 @@
         <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="AP50">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ50">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR50">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AS50">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AT50">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11616,25 +11616,25 @@
         <v>1.4</v>
       </c>
       <c r="AN51">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO51">
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ51">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR51">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AS51">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AT51">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AU51">
         <v>3</v>
@@ -11822,25 +11822,25 @@
         <v>2.49</v>
       </c>
       <c r="AN52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO52">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP52">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR52">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AS52">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AT52">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AU52">
         <v>12</v>
@@ -12028,25 +12028,25 @@
         <v>1.2</v>
       </c>
       <c r="AN53">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ53">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR53">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AS53">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="AT53">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="AU53">
         <v>6</v>
@@ -12234,25 +12234,25 @@
         <v>1.24</v>
       </c>
       <c r="AN54">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="AO54">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ54">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR54">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AS54">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT54">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12443,19 +12443,19 @@
         <v>1</v>
       </c>
       <c r="AO55">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="AP55">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ55">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR55">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AS55">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AT55">
         <v>3.05</v>
@@ -12649,22 +12649,22 @@
         <v>2</v>
       </c>
       <c r="AO56">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP56">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ56">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR56">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AS56">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AT56">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12852,25 +12852,25 @@
         <v>1.68</v>
       </c>
       <c r="AN57">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AO57">
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR57">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AS57">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AT57">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13058,25 +13058,25 @@
         <v>1.68</v>
       </c>
       <c r="AN58">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO58">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AP58">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR58">
-        <v>2.03</v>
+        <v>1.74</v>
       </c>
       <c r="AS58">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AT58">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13264,25 +13264,25 @@
         <v>1.46</v>
       </c>
       <c r="AN59">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO59">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP59">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ59">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR59">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AS59">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AT59">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13470,25 +13470,25 @@
         <v>1.45</v>
       </c>
       <c r="AN60">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP60">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ60">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR60">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AS60">
-        <v>1.23</v>
+        <v>1.78</v>
       </c>
       <c r="AT60">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13676,22 +13676,22 @@
         <v>2.6</v>
       </c>
       <c r="AN61">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO61">
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR61">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AS61">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AT61">
         <v>3.27</v>
@@ -13882,25 +13882,25 @@
         <v>1.71</v>
       </c>
       <c r="AN62">
-        <v>0.33</v>
+        <v>1.14</v>
       </c>
       <c r="AO62">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP62">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ62">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR62">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AS62">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AT62">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14088,25 +14088,25 @@
         <v>1.94</v>
       </c>
       <c r="AN63">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AO63">
-        <v>0.75</v>
+        <v>1.71</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ63">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR63">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="AS63">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AT63">
-        <v>2.67</v>
+        <v>2.37</v>
       </c>
       <c r="AU63">
         <v>3</v>
@@ -14297,22 +14297,22 @@
         <v>1</v>
       </c>
       <c r="AO64">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="AP64">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ64">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR64">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AS64">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="AT64">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14500,25 +14500,25 @@
         <v>1.95</v>
       </c>
       <c r="AN65">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO65">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ65">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR65">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AS65">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AT65">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14706,25 +14706,25 @@
         <v>1.25</v>
       </c>
       <c r="AN66">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="AO66">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ66">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR66">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AS66">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AT66">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14912,25 +14912,25 @@
         <v>1.4</v>
       </c>
       <c r="AN67">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AO67">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP67">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ67">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR67">
-        <v>0.97</v>
+        <v>1.18</v>
       </c>
       <c r="AS67">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT67">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -15118,25 +15118,25 @@
         <v>1.25</v>
       </c>
       <c r="AN68">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO68">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AP68">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ68">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR68">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AS68">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AT68">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15324,25 +15324,25 @@
         <v>1.57</v>
       </c>
       <c r="AN69">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AO69">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AP69">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR69">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AS69">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AT69">
-        <v>3.32</v>
+        <v>3.59</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15530,25 +15530,25 @@
         <v>1.5</v>
       </c>
       <c r="AN70">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AP70">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ70">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR70">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AS70">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT70">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AU70">
         <v>3</v>
@@ -15736,25 +15736,25 @@
         <v>1.78</v>
       </c>
       <c r="AN71">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AO71">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AP71">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR71">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS71">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AT71">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="AU71">
         <v>4</v>
@@ -15942,25 +15942,25 @@
         <v>1.8</v>
       </c>
       <c r="AN72">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AO72">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP72">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ72">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR72">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="AS72">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT72">
-        <v>2.91</v>
+        <v>2.57</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16148,25 +16148,25 @@
         <v>1.62</v>
       </c>
       <c r="AN73">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO73">
-        <v>0.6</v>
+        <v>1.67</v>
       </c>
       <c r="AP73">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ73">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR73">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AS73">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT73">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16354,25 +16354,25 @@
         <v>1.25</v>
       </c>
       <c r="AN74">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AO74">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP74">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ74">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR74">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS74">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AT74">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="AU74">
         <v>2</v>
@@ -16560,25 +16560,25 @@
         <v>2.45</v>
       </c>
       <c r="AN75">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AO75">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP75">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AQ75">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR75">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AS75">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AT75">
-        <v>3.43</v>
+        <v>3.03</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16766,25 +16766,25 @@
         <v>1.62</v>
       </c>
       <c r="AN76">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO76">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AP76">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ76">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR76">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS76">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AT76">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16972,25 +16972,25 @@
         <v>1.53</v>
       </c>
       <c r="AN77">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO77">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ77">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR77">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AS77">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AT77">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17178,25 +17178,25 @@
         <v>1.71</v>
       </c>
       <c r="AN78">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AO78">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="AP78">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR78">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AS78">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AT78">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17384,25 +17384,25 @@
         <v>1.22</v>
       </c>
       <c r="AN79">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AO79">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP79">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ79">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR79">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AS79">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AT79">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17590,25 +17590,25 @@
         <v>1.57</v>
       </c>
       <c r="AN80">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO80">
-        <v>0.25</v>
+        <v>1.3</v>
       </c>
       <c r="AP80">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ80">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR80">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AS80">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT80">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AU80">
         <v>10</v>
@@ -17796,25 +17796,25 @@
         <v>1.9</v>
       </c>
       <c r="AN81">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AO81">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ81">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR81">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AS81">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AT81">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -18002,25 +18002,25 @@
         <v>1.3</v>
       </c>
       <c r="AN82">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AO82">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AP82">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ82">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR82">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AS82">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AT82">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AU82">
         <v>2</v>
@@ -18211,22 +18211,22 @@
         <v>1.67</v>
       </c>
       <c r="AO83">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="AP83">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ83">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR83">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AS83">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AT83">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18414,25 +18414,25 @@
         <v>1.95</v>
       </c>
       <c r="AN84">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AO84">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AP84">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ84">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR84">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS84">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AT84">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AU84">
         <v>2</v>
@@ -18620,25 +18620,25 @@
         <v>1.25</v>
       </c>
       <c r="AN85">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AO85">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ85">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR85">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS85">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AT85">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18826,25 +18826,25 @@
         <v>1.44</v>
       </c>
       <c r="AN86">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AO86">
-        <v>0.67</v>
+        <v>1.11</v>
       </c>
       <c r="AP86">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR86">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AS86">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="AT86">
-        <v>2.99</v>
+        <v>3.39</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -19032,25 +19032,25 @@
         <v>2.9</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AO87">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AP87">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ87">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR87">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AS87">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AT87">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19238,25 +19238,25 @@
         <v>1.52</v>
       </c>
       <c r="AN88">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AO88">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP88">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ88">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR88">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AS88">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT88">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19444,22 +19444,22 @@
         <v>1.86</v>
       </c>
       <c r="AN89">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AO89">
-        <v>0.67</v>
+        <v>1.55</v>
       </c>
       <c r="AP89">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ89">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR89">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AS89">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT89">
         <v>2.69</v>
@@ -19650,25 +19650,25 @@
         <v>1.24</v>
       </c>
       <c r="AN90">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AP90">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ90">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR90">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS90">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AT90">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19856,25 +19856,25 @@
         <v>2.7</v>
       </c>
       <c r="AN91">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AO91">
-        <v>0.8</v>
+        <v>1.27</v>
       </c>
       <c r="AP91">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR91">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AS91">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AT91">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20062,25 +20062,25 @@
         <v>1.37</v>
       </c>
       <c r="AN92">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO92">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AP92">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ92">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR92">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS92">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AT92">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20268,25 +20268,25 @@
         <v>1.44</v>
       </c>
       <c r="AN93">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="AO93">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ93">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR93">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AS93">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AT93">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20474,25 +20474,25 @@
         <v>1.29</v>
       </c>
       <c r="AN94">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO94">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AP94">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ94">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR94">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AS94">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT94">
-        <v>3.34</v>
+        <v>2.85</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -20680,25 +20680,25 @@
         <v>3.15</v>
       </c>
       <c r="AN95">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AO95">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="AP95">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AQ95">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR95">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AS95">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AT95">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AU95">
         <v>9</v>
@@ -20886,25 +20886,25 @@
         <v>1.42</v>
       </c>
       <c r="AN96">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AO96">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ96">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR96">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AS96">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AT96">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="AU96">
         <v>9</v>
@@ -21092,25 +21092,25 @@
         <v>1.78</v>
       </c>
       <c r="AN97">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AO97">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ97">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR97">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AS97">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AT97">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21301,22 +21301,22 @@
         <v>1.17</v>
       </c>
       <c r="AO98">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AP98">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR98">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AS98">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AT98">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21504,25 +21504,25 @@
         <v>1.15</v>
       </c>
       <c r="AN99">
+        <v>1.5</v>
+      </c>
+      <c r="AO99">
+        <v>1.64</v>
+      </c>
+      <c r="AP99">
+        <v>1.48</v>
+      </c>
+      <c r="AQ99">
         <v>1.67</v>
       </c>
-      <c r="AO99">
-        <v>1.67</v>
-      </c>
-      <c r="AP99">
-        <v>1.64</v>
-      </c>
-      <c r="AQ99">
-        <v>1.7</v>
-      </c>
       <c r="AR99">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AS99">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AT99">
-        <v>2.86</v>
+        <v>3.07</v>
       </c>
       <c r="AU99">
         <v>0</v>
@@ -21710,25 +21710,25 @@
         <v>2.85</v>
       </c>
       <c r="AN100">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AO100">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP100">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR100">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AS100">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AT100">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21916,25 +21916,25 @@
         <v>1.2</v>
       </c>
       <c r="AN101">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO101">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ101">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR101">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AS101">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AT101">
-        <v>2.58</v>
+        <v>2.91</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22122,25 +22122,25 @@
         <v>1.87</v>
       </c>
       <c r="AN102">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AO102">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP102">
+        <v>1.05</v>
+      </c>
+      <c r="AQ102">
+        <v>1.05</v>
+      </c>
+      <c r="AR102">
         <v>1.55</v>
       </c>
-      <c r="AQ102">
-        <v>1.18</v>
-      </c>
-      <c r="AR102">
-        <v>1.5</v>
-      </c>
       <c r="AS102">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AT102">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22328,25 +22328,25 @@
         <v>1.72</v>
       </c>
       <c r="AN103">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AO103">
-        <v>0.6</v>
+        <v>1.08</v>
       </c>
       <c r="AP103">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ103">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR103">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AS103">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AT103">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22534,25 +22534,25 @@
         <v>1.95</v>
       </c>
       <c r="AN104">
+        <v>1.58</v>
+      </c>
+      <c r="AO104">
+        <v>1.31</v>
+      </c>
+      <c r="AP104">
+        <v>1.67</v>
+      </c>
+      <c r="AQ104">
+        <v>1.43</v>
+      </c>
+      <c r="AR104">
+        <v>1.68</v>
+      </c>
+      <c r="AS104">
         <v>1.63</v>
       </c>
-      <c r="AO104">
-        <v>1.17</v>
-      </c>
-      <c r="AP104">
-        <v>1.64</v>
-      </c>
-      <c r="AQ104">
-        <v>1.2</v>
-      </c>
-      <c r="AR104">
-        <v>1.78</v>
-      </c>
-      <c r="AS104">
-        <v>1.74</v>
-      </c>
       <c r="AT104">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="AU104">
         <v>9</v>
@@ -22740,25 +22740,25 @@
         <v>1.95</v>
       </c>
       <c r="AN105">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AO105">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP105">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ105">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR105">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AS105">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AT105">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -22946,25 +22946,25 @@
         <v>1.66</v>
       </c>
       <c r="AN106">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AO106">
-        <v>0.67</v>
+        <v>1.31</v>
       </c>
       <c r="AP106">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR106">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AS106">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AT106">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="AU106">
         <v>11</v>
@@ -23152,25 +23152,25 @@
         <v>1.55</v>
       </c>
       <c r="AN107">
+        <v>1</v>
+      </c>
+      <c r="AO107">
+        <v>1.38</v>
+      </c>
+      <c r="AP107">
+        <v>1.24</v>
+      </c>
+      <c r="AQ107">
         <v>1.71</v>
       </c>
-      <c r="AO107">
-        <v>0.71</v>
-      </c>
-      <c r="AP107">
-        <v>1.73</v>
-      </c>
-      <c r="AQ107">
-        <v>1.4</v>
-      </c>
       <c r="AR107">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AS107">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AT107">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AU107">
         <v>4</v>
@@ -23358,25 +23358,25 @@
         <v>1.97</v>
       </c>
       <c r="AN108">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AO108">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP108">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ108">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR108">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AS108">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AT108">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="AU108">
         <v>0</v>
@@ -23564,25 +23564,25 @@
         <v>2</v>
       </c>
       <c r="AN109">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AO109">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AP109">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AQ109">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR109">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AS109">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AT109">
-        <v>3.51</v>
+        <v>3.21</v>
       </c>
       <c r="AU109">
         <v>7</v>
@@ -23770,25 +23770,25 @@
         <v>1.32</v>
       </c>
       <c r="AN110">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO110">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AP110">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ110">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR110">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AS110">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AT110">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="AU110">
         <v>3</v>
@@ -23976,25 +23976,25 @@
         <v>1.34</v>
       </c>
       <c r="AN111">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO111">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AP111">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ111">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR111">
+        <v>1.49</v>
+      </c>
+      <c r="AS111">
         <v>1.65</v>
       </c>
-      <c r="AS111">
-        <v>1.42</v>
-      </c>
       <c r="AT111">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="AU111">
         <v>5</v>
@@ -24182,25 +24182,25 @@
         <v>1.08</v>
       </c>
       <c r="AN112">
-        <v>1.33</v>
+        <v>0.93</v>
       </c>
       <c r="AO112">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ112">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR112">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AS112">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="AT112">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="AU112">
         <v>3</v>
@@ -24388,25 +24388,25 @@
         <v>1.8</v>
       </c>
       <c r="AN113">
+        <v>1.29</v>
+      </c>
+      <c r="AO113">
+        <v>1.57</v>
+      </c>
+      <c r="AP113">
         <v>1.43</v>
       </c>
-      <c r="AO113">
-        <v>1.33</v>
-      </c>
-      <c r="AP113">
-        <v>1.64</v>
-      </c>
       <c r="AQ113">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR113">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AS113">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT113">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24594,25 +24594,25 @@
         <v>1.8</v>
       </c>
       <c r="AN114">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AO114">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR114">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AS114">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AT114">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="AU114">
         <v>4</v>
@@ -24800,25 +24800,25 @@
         <v>1.42</v>
       </c>
       <c r="AN115">
-        <v>1.86</v>
+        <v>1.21</v>
       </c>
       <c r="AO115">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AP115">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ115">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR115">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS115">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT115">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -25006,25 +25006,25 @@
         <v>1.9</v>
       </c>
       <c r="AN116">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="AO116">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ116">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR116">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AS116">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AT116">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU116">
         <v>4</v>
@@ -25212,25 +25212,25 @@
         <v>1.62</v>
       </c>
       <c r="AN117">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO117">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AP117">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ117">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR117">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AS117">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AT117">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AU117">
         <v>4</v>
@@ -25418,25 +25418,25 @@
         <v>1.5</v>
       </c>
       <c r="AN118">
-        <v>0.83</v>
+        <v>1.07</v>
       </c>
       <c r="AO118">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="AP118">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ118">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR118">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AS118">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AT118">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25624,25 +25624,25 @@
         <v>2.2</v>
       </c>
       <c r="AN119">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AO119">
-        <v>0.17</v>
+        <v>0.93</v>
       </c>
       <c r="AP119">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ119">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR119">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AS119">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AT119">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25830,25 +25830,25 @@
         <v>1.76</v>
       </c>
       <c r="AN120">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AO120">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="AP120">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ120">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR120">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AS120">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AT120">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -26036,25 +26036,25 @@
         <v>1.36</v>
       </c>
       <c r="AN121">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="AO121">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ121">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR121">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AS121">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AT121">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26242,25 +26242,25 @@
         <v>1.36</v>
       </c>
       <c r="AN122">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO122">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AP122">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ122">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR122">
+        <v>1.49</v>
+      </c>
+      <c r="AS122">
         <v>1.54</v>
       </c>
-      <c r="AS122">
-        <v>1.62</v>
-      </c>
       <c r="AT122">
-        <v>3.16</v>
+        <v>3.03</v>
       </c>
       <c r="AU122">
         <v>3</v>
@@ -26448,25 +26448,25 @@
         <v>2.2</v>
       </c>
       <c r="AN123">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="AO123">
-        <v>0.14</v>
+        <v>0.87</v>
       </c>
       <c r="AP123">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ123">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR123">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AS123">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AT123">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="AU123">
         <v>8</v>
@@ -26654,25 +26654,25 @@
         <v>1.99</v>
       </c>
       <c r="AN124">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AO124">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AP124">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR124">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS124">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AT124">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AU124">
         <v>13</v>
@@ -26860,25 +26860,25 @@
         <v>1.44</v>
       </c>
       <c r="AN125">
+        <v>1.2</v>
+      </c>
+      <c r="AO125">
+        <v>1.13</v>
+      </c>
+      <c r="AP125">
+        <v>1.05</v>
+      </c>
+      <c r="AQ125">
         <v>1.14</v>
       </c>
-      <c r="AO125">
-        <v>0.57</v>
-      </c>
-      <c r="AP125">
-        <v>0.9</v>
-      </c>
-      <c r="AQ125">
-        <v>0.91</v>
-      </c>
       <c r="AR125">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AS125">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AT125">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -27066,25 +27066,25 @@
         <v>1.41</v>
       </c>
       <c r="AN126">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AO126">
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ126">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR126">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS126">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AT126">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27272,25 +27272,25 @@
         <v>1.36</v>
       </c>
       <c r="AN127">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="AO127">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ127">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR127">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AS127">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AT127">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27478,25 +27478,25 @@
         <v>1.33</v>
       </c>
       <c r="AN128">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AO128">
+        <v>1.6</v>
+      </c>
+      <c r="AP128">
+        <v>1.14</v>
+      </c>
+      <c r="AQ128">
         <v>1.67</v>
       </c>
-      <c r="AP128">
-        <v>1.1</v>
-      </c>
-      <c r="AQ128">
-        <v>1.7</v>
-      </c>
       <c r="AR128">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS128">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="AT128">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="AU128">
         <v>3</v>
@@ -27684,25 +27684,25 @@
         <v>1.17</v>
       </c>
       <c r="AN129">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="AO129">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AP129">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ129">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR129">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AS129">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="AT129">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AU129">
         <v>5</v>
@@ -27893,22 +27893,22 @@
         <v>1.38</v>
       </c>
       <c r="AO130">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP130">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ130">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR130">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AS130">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AT130">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28096,25 +28096,25 @@
         <v>1.56</v>
       </c>
       <c r="AN131">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AO131">
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ131">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR131">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AS131">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AT131">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="AU131">
         <v>0</v>
@@ -28302,25 +28302,25 @@
         <v>1.28</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AO132">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AP132">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ132">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR132">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS132">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AT132">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AU132">
         <v>5</v>
@@ -28508,25 +28508,25 @@
         <v>1.7</v>
       </c>
       <c r="AN133">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AO133">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AP133">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ133">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR133">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AS133">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT133">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="AU133">
         <v>3</v>
@@ -28717,22 +28717,22 @@
         <v>1.5</v>
       </c>
       <c r="AO134">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AP134">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AQ134">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR134">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AS134">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AT134">
-        <v>3.33</v>
+        <v>3.09</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -28920,25 +28920,25 @@
         <v>1.62</v>
       </c>
       <c r="AN135">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO135">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP135">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ135">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR135">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS135">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AT135">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29126,25 +29126,25 @@
         <v>1.46</v>
       </c>
       <c r="AN136">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="AO136">
-        <v>0.57</v>
+        <v>1.25</v>
       </c>
       <c r="AP136">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ136">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR136">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AS136">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AT136">
-        <v>3.17</v>
+        <v>2.89</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29332,25 +29332,25 @@
         <v>1.25</v>
       </c>
       <c r="AN137">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AP137">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ137">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR137">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="AS137">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AT137">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AU137">
         <v>6</v>
@@ -29538,25 +29538,25 @@
         <v>1.34</v>
       </c>
       <c r="AN138">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AO138">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="AP138">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ138">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR138">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AS138">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AT138">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AU138">
         <v>4</v>
@@ -29744,25 +29744,25 @@
         <v>1.72</v>
       </c>
       <c r="AN139">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AO139">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AP139">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ139">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR139">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AS139">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT139">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="AU139">
         <v>6</v>
@@ -29950,25 +29950,25 @@
         <v>1.37</v>
       </c>
       <c r="AN140">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AO140">
-        <v>0.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP140">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ140">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR140">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AS140">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT140">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="AU140">
         <v>7</v>
@@ -30156,25 +30156,25 @@
         <v>1.42</v>
       </c>
       <c r="AN141">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AO141">
-        <v>0.63</v>
+        <v>1.24</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ141">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR141">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS141">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AT141">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AU141">
         <v>7</v>
@@ -30362,25 +30362,25 @@
         <v>1.47</v>
       </c>
       <c r="AN142">
-        <v>2.13</v>
+        <v>1.65</v>
       </c>
       <c r="AO142">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ142">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR142">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AS142">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AT142">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AU142">
         <v>4</v>
@@ -30568,25 +30568,25 @@
         <v>1.42</v>
       </c>
       <c r="AN143">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AO143">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AP143">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ143">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR143">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AS143">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AT143">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30774,25 +30774,25 @@
         <v>1.83</v>
       </c>
       <c r="AN144">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AO144">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ144">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR144">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AS144">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AT144">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AU144">
         <v>8</v>
@@ -30980,25 +30980,25 @@
         <v>1.21</v>
       </c>
       <c r="AN145">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AO145">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AP145">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ145">
+        <v>1.76</v>
+      </c>
+      <c r="AR145">
+        <v>1.37</v>
+      </c>
+      <c r="AS145">
         <v>1.73</v>
       </c>
-      <c r="AR145">
-        <v>1.39</v>
-      </c>
-      <c r="AS145">
-        <v>1.41</v>
-      </c>
       <c r="AT145">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AU145">
         <v>4</v>
@@ -31186,25 +31186,25 @@
         <v>1.41</v>
       </c>
       <c r="AN146">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AO146">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AP146">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ146">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR146">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AS146">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AT146">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="AU146">
         <v>5</v>
@@ -31392,25 +31392,25 @@
         <v>1.32</v>
       </c>
       <c r="AN147">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AO147">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="AQ147">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AR147">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AS147">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT147">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31598,25 +31598,25 @@
         <v>1.27</v>
       </c>
       <c r="AN148">
+        <v>1.5</v>
+      </c>
+      <c r="AO148">
         <v>1.56</v>
       </c>
-      <c r="AO148">
-        <v>1.33</v>
-      </c>
       <c r="AP148">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AQ148">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AR148">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AS148">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AT148">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AU148">
         <v>4</v>
@@ -31804,25 +31804,25 @@
         <v>1.64</v>
       </c>
       <c r="AN149">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO149">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ149">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AR149">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AS149">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AT149">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -32010,25 +32010,25 @@
         <v>1.42</v>
       </c>
       <c r="AN150">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="AO150">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="AP150">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ150">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR150">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AS150">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AT150">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="AU150">
         <v>5</v>
@@ -32219,22 +32219,22 @@
         <v>1.67</v>
       </c>
       <c r="AO151">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP151">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AQ151">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR151">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AS151">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AT151">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="AU151">
         <v>9</v>
@@ -32422,25 +32422,25 @@
         <v>1.38</v>
       </c>
       <c r="AN152">
-        <v>1.67</v>
+        <v>1.06</v>
       </c>
       <c r="AO152">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AP152">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ152">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR152">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AS152">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AT152">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="AU152">
         <v>5</v>
@@ -32628,25 +32628,25 @@
         <v>1.35</v>
       </c>
       <c r="AN153">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO153">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ153">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR153">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AS153">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AT153">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AU153">
         <v>6</v>
@@ -32834,25 +32834,25 @@
         <v>1.44</v>
       </c>
       <c r="AN154">
-        <v>1.33</v>
+        <v>0.95</v>
       </c>
       <c r="AO154">
-        <v>0.44</v>
+        <v>1.16</v>
       </c>
       <c r="AP154">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AQ154">
-        <v>0.7</v>
+        <v>1.24</v>
       </c>
       <c r="AR154">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AS154">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AT154">
-        <v>2.99</v>
+        <v>2.67</v>
       </c>
       <c r="AU154">
         <v>5</v>
@@ -33040,25 +33040,25 @@
         <v>1.78</v>
       </c>
       <c r="AN155">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AO155">
-        <v>0.5600000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
       </c>
       <c r="AS155">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AT155">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AU155">
         <v>8</v>
@@ -33246,25 +33246,25 @@
         <v>1.66</v>
       </c>
       <c r="AN156">
+        <v>1.21</v>
+      </c>
+      <c r="AO156">
         <v>1.11</v>
       </c>
-      <c r="AO156">
-        <v>1</v>
-      </c>
       <c r="AP156">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AR156">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS156">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AT156">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AU156">
         <v>4</v>
@@ -33452,25 +33452,25 @@
         <v>1.68</v>
       </c>
       <c r="AN157">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AO157">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AP157">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AQ157">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AR157">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AS157">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AT157">
-        <v>3.31</v>
+        <v>3.16</v>
       </c>
       <c r="AU157">
         <v>7</v>
@@ -33658,25 +33658,25 @@
         <v>1.65</v>
       </c>
       <c r="AN158">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AO158">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AP158">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AQ158">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AR158">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS158">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AT158">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="AU158">
         <v>7</v>
@@ -33864,25 +33864,25 @@
         <v>1.17</v>
       </c>
       <c r="AN159">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="AO159">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AP159">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AQ159">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AR159">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AS159">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AT159">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="AU159">
         <v>3</v>
@@ -34070,25 +34070,25 @@
         <v>1.27</v>
       </c>
       <c r="AN160">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AO160">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AP160">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AQ160">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR160">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS160">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AT160">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AU160">
         <v>7</v>
@@ -34276,25 +34276,25 @@
         <v>2.29</v>
       </c>
       <c r="AN161">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AO161">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="AP161">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AQ161">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AR161">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AS161">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AT161">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34482,25 +34482,25 @@
         <v>1.43</v>
       </c>
       <c r="AN162">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AO162">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AP162">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AQ162">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AR162">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AS162">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AT162">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AU162">
         <v>0</v>
@@ -34688,25 +34688,25 @@
         <v>1.55</v>
       </c>
       <c r="AN163">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO163">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
       <c r="AP163">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AQ163">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="AR163">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AS163">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AT163">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="AU163">
         <v>3</v>
@@ -34894,25 +34894,25 @@
         <v>1.16</v>
       </c>
       <c r="AN164">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AO164">
+        <v>1.6</v>
+      </c>
+      <c r="AP164">
+        <v>0.76</v>
+      </c>
+      <c r="AQ164">
+        <v>1.67</v>
+      </c>
+      <c r="AR164">
         <v>1.3</v>
       </c>
-      <c r="AP164">
-        <v>1</v>
-      </c>
-      <c r="AQ164">
-        <v>1.45</v>
-      </c>
-      <c r="AR164">
-        <v>1.45</v>
-      </c>
       <c r="AS164">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AT164">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="AU164">
         <v>5</v>
@@ -35100,25 +35100,25 @@
         <v>1.8</v>
       </c>
       <c r="AN165">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO165">
+        <v>1.1</v>
+      </c>
+      <c r="AP165">
+        <v>1.48</v>
+      </c>
+      <c r="AQ165">
+        <v>1.05</v>
+      </c>
+      <c r="AR165">
         <v>1.3</v>
       </c>
-      <c r="AP165">
-        <v>1.64</v>
-      </c>
-      <c r="AQ165">
-        <v>1.18</v>
-      </c>
-      <c r="AR165">
-        <v>1.27</v>
-      </c>
       <c r="AS165">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AT165">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35306,25 +35306,25 @@
         <v>1.94</v>
       </c>
       <c r="AN166">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO166">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AP166">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ166">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AR166">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AS166">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AT166">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU166">
         <v>5</v>
@@ -35512,25 +35512,25 @@
         <v>1.37</v>
       </c>
       <c r="AN167">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AO167">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AP167">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ167">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AR167">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AS167">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AT167">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35718,25 +35718,25 @@
         <v>1.59</v>
       </c>
       <c r="AN168">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AO168">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="AP168">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AQ168">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="AR168">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AS168">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AT168">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AU168">
         <v>7</v>
@@ -35924,25 +35924,25 @@
         <v>1.19</v>
       </c>
       <c r="AN169">
+        <v>1.1</v>
+      </c>
+      <c r="AO169">
         <v>1.7</v>
       </c>
-      <c r="AO169">
-        <v>1.6</v>
-      </c>
       <c r="AP169">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AQ169">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AR169">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AS169">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AT169">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="AU169">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="277">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,6 +595,12 @@
     <t>['42', '77']</t>
   </si>
   <si>
+    <t>['8', '28', '78']</t>
+  </si>
+  <si>
+    <t>['84', '90+1']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -833,6 +839,12 @@
   </si>
   <si>
     <t>['44', '76']</t>
+  </si>
+  <si>
+    <t>['51', '69']</t>
+  </si>
+  <si>
+    <t>['35']</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1450,7 +1462,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1528,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ2">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1734,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ3">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1940,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AQ4">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2146,10 +2158,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ5">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2274,7 +2286,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q6">
         <v>2.25</v>
@@ -2352,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ6">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2480,7 +2492,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2558,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2686,7 +2698,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2764,10 +2776,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2970,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ9">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3176,19 +3188,19 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ10">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR10">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -3304,7 +3316,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3376,25 +3388,25 @@
         <v>1.13</v>
       </c>
       <c r="AN11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ11">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR11">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3510,7 +3522,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3582,25 +3594,25 @@
         <v>2.1</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ12">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR12">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>9</v>
@@ -3716,7 +3728,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3788,25 +3800,25 @@
         <v>1.4</v>
       </c>
       <c r="AN13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ13">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR13">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -3922,7 +3934,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -3994,25 +4006,25 @@
         <v>1.72</v>
       </c>
       <c r="AN14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ14">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR14">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4128,7 +4140,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4203,22 +4215,22 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR15">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>5</v>
@@ -4334,7 +4346,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4406,25 +4418,25 @@
         <v>1.3</v>
       </c>
       <c r="AN16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR16">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>7</v>
@@ -4612,25 +4624,25 @@
         <v>1.55</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ17">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR17">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>3</v>
@@ -4746,7 +4758,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4818,25 +4830,25 @@
         <v>1.8</v>
       </c>
       <c r="AN18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ18">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR18">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="AS18">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AT18">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AU18">
         <v>2</v>
@@ -4952,7 +4964,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5027,22 +5039,22 @@
         <v>1</v>
       </c>
       <c r="AO19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ19">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR19">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AS19">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AT19">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="AU19">
         <v>8</v>
@@ -5158,7 +5170,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5230,25 +5242,25 @@
         <v>1.6</v>
       </c>
       <c r="AN20">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ20">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR20">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AS20">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="AT20">
-        <v>2.83</v>
+        <v>2.16</v>
       </c>
       <c r="AU20">
         <v>4</v>
@@ -5439,22 +5451,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AQ21">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR21">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AS21">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="AT21">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="AU21">
         <v>2</v>
@@ -5570,7 +5582,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5642,25 +5654,25 @@
         <v>2.35</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR22">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AS22">
-        <v>1.18</v>
+        <v>0.77</v>
       </c>
       <c r="AT22">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="AU22">
         <v>2</v>
@@ -5776,7 +5788,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -5848,25 +5860,25 @@
         <v>1.95</v>
       </c>
       <c r="AN23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ23">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR23">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AS23">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AT23">
-        <v>3.77</v>
+        <v>4.23</v>
       </c>
       <c r="AU23">
         <v>3</v>
@@ -6054,25 +6066,25 @@
         <v>1.36</v>
       </c>
       <c r="AN24">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR24">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AS24">
-        <v>1.06</v>
+        <v>0.54</v>
       </c>
       <c r="AT24">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="AU24">
         <v>5</v>
@@ -6260,25 +6272,25 @@
         <v>1.26</v>
       </c>
       <c r="AN25">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO25">
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ25">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR25">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="AS25">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AT25">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="AU25">
         <v>3</v>
@@ -6466,25 +6478,25 @@
         <v>1.63</v>
       </c>
       <c r="AN26">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ26">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR26">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AS26">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AT26">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AU26">
         <v>5</v>
@@ -6672,25 +6684,25 @@
         <v>1.75</v>
       </c>
       <c r="AN27">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR27">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AS27">
-        <v>1.22</v>
+        <v>0.99</v>
       </c>
       <c r="AT27">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AU27">
         <v>7</v>
@@ -6878,25 +6890,25 @@
         <v>2.25</v>
       </c>
       <c r="AN28">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ28">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR28">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AS28">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AT28">
-        <v>3.31</v>
+        <v>3.56</v>
       </c>
       <c r="AU28">
         <v>6</v>
@@ -7084,25 +7096,25 @@
         <v>2.35</v>
       </c>
       <c r="AN29">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ29">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR29">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="AS29">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="AT29">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AU29">
         <v>0</v>
@@ -7218,7 +7230,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7290,25 +7302,25 @@
         <v>1.66</v>
       </c>
       <c r="AN30">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO30">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ30">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR30">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AS30">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="AT30">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="AU30">
         <v>7</v>
@@ -7424,7 +7436,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7496,25 +7508,25 @@
         <v>1.45</v>
       </c>
       <c r="AN31">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ31">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR31">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AS31">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AT31">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="AU31">
         <v>3</v>
@@ -7630,7 +7642,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7702,25 +7714,25 @@
         <v>1.72</v>
       </c>
       <c r="AN32">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ32">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR32">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AS32">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AT32">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="AU32">
         <v>5</v>
@@ -7836,7 +7848,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -7908,25 +7920,25 @@
         <v>2</v>
       </c>
       <c r="AN33">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO33">
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ33">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR33">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AS33">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AT33">
-        <v>3.46</v>
+        <v>3.79</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8042,7 +8054,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8114,25 +8126,25 @@
         <v>1.68</v>
       </c>
       <c r="AN34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ34">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR34">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AS34">
-        <v>1.13</v>
+        <v>0.9</v>
       </c>
       <c r="AT34">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AU34">
         <v>3</v>
@@ -8248,7 +8260,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8320,25 +8332,25 @@
         <v>1.47</v>
       </c>
       <c r="AN35">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AO35">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ35">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR35">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AS35">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AT35">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="AU35">
         <v>8</v>
@@ -8454,7 +8466,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -8526,25 +8538,25 @@
         <v>1.25</v>
       </c>
       <c r="AN36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR36">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AS36">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AT36">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AU36">
         <v>4</v>
@@ -8660,7 +8672,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8738,19 +8750,19 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AQ37">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR37">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="AS37">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AT37">
-        <v>3.39</v>
+        <v>3.17</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -8941,22 +8953,22 @@
         <v>1</v>
       </c>
       <c r="AO38">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ38">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR38">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AS38">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AT38">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="AU38">
         <v>7</v>
@@ -9144,25 +9156,25 @@
         <v>1.34</v>
       </c>
       <c r="AN39">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP39">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ39">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR39">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS39">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AT39">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9278,7 +9290,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9350,25 +9362,25 @@
         <v>1.44</v>
       </c>
       <c r="AN40">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO40">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ40">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR40">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AS40">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AT40">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AU40">
         <v>7</v>
@@ -9484,7 +9496,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9556,25 +9568,25 @@
         <v>1.57</v>
       </c>
       <c r="AN41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO41">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ41">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR41">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT41">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="AU41">
         <v>7</v>
@@ -9690,7 +9702,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9762,25 +9774,25 @@
         <v>2.35</v>
       </c>
       <c r="AN42">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AO42">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ42">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR42">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AS42">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AT42">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="AU42">
         <v>12</v>
@@ -9968,25 +9980,25 @@
         <v>1.7</v>
       </c>
       <c r="AN43">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AO43">
+        <v>1.5</v>
+      </c>
+      <c r="AP43">
         <v>1.2</v>
       </c>
-      <c r="AP43">
-        <v>0.86</v>
-      </c>
       <c r="AQ43">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR43">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="AS43">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="AT43">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AU43">
         <v>4</v>
@@ -10174,25 +10186,25 @@
         <v>2.6</v>
       </c>
       <c r="AN44">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO44">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ44">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AS44">
         <v>1.49</v>
       </c>
       <c r="AT44">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="AU44">
         <v>3</v>
@@ -10380,25 +10392,25 @@
         <v>2</v>
       </c>
       <c r="AN45">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO45">
-        <v>1.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ45">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR45">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AS45">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AT45">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="AU45">
         <v>4</v>
@@ -10586,25 +10598,25 @@
         <v>1.62</v>
       </c>
       <c r="AN46">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP46">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ46">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR46">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AS46">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AT46">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="AU46">
         <v>8</v>
@@ -10720,7 +10732,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10792,25 +10804,25 @@
         <v>2.02</v>
       </c>
       <c r="AN47">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ47">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR47">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AS47">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AT47">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AU47">
         <v>9</v>
@@ -10998,25 +11010,25 @@
         <v>1.45</v>
       </c>
       <c r="AN48">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO48">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AP48">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ48">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR48">
-        <v>1.12</v>
+        <v>0.93</v>
       </c>
       <c r="AS48">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AT48">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="AU48">
         <v>3</v>
@@ -11132,7 +11144,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11204,25 +11216,25 @@
         <v>1.36</v>
       </c>
       <c r="AN49">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO49">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AP49">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ49">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR49">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AS49">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AT49">
-        <v>2.92</v>
+        <v>3.09</v>
       </c>
       <c r="AU49">
         <v>9</v>
@@ -11413,22 +11425,22 @@
         <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="AP50">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AQ50">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR50">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AS50">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AT50">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11616,25 +11628,25 @@
         <v>1.4</v>
       </c>
       <c r="AN51">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO51">
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR51">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AS51">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AT51">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AU51">
         <v>3</v>
@@ -11822,25 +11834,25 @@
         <v>2.49</v>
       </c>
       <c r="AN52">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO52">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ52">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR52">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AS52">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AT52">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AU52">
         <v>12</v>
@@ -12028,25 +12040,25 @@
         <v>1.2</v>
       </c>
       <c r="AN53">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="AO53">
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ53">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR53">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AS53">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="AT53">
-        <v>3.01</v>
+        <v>2.36</v>
       </c>
       <c r="AU53">
         <v>6</v>
@@ -12162,7 +12174,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12234,25 +12246,25 @@
         <v>1.24</v>
       </c>
       <c r="AN54">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="AO54">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR54">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AS54">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT54">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="AU54">
         <v>4</v>
@@ -12368,7 +12380,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12443,19 +12455,19 @@
         <v>1</v>
       </c>
       <c r="AO55">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ55">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR55">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AS55">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="AT55">
         <v>3.05</v>
@@ -12649,22 +12661,22 @@
         <v>2</v>
       </c>
       <c r="AO56">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AP56">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ56">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR56">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AS56">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AT56">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="AU56">
         <v>7</v>
@@ -12780,7 +12792,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12852,25 +12864,25 @@
         <v>1.68</v>
       </c>
       <c r="AN57">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AO57">
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR57">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AS57">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT57">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AU57">
         <v>8</v>
@@ -13058,25 +13070,25 @@
         <v>1.68</v>
       </c>
       <c r="AN58">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO58">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AP58">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ58">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR58">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AS58">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AT58">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="AU58">
         <v>4</v>
@@ -13192,7 +13204,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13264,25 +13276,25 @@
         <v>1.46</v>
       </c>
       <c r="AN59">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO59">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ59">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR59">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AS59">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AT59">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="AU59">
         <v>4</v>
@@ -13398,7 +13410,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13470,25 +13482,25 @@
         <v>1.45</v>
       </c>
       <c r="AN60">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AO60">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ60">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR60">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AS60">
-        <v>1.78</v>
+        <v>1.23</v>
       </c>
       <c r="AT60">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AU60">
         <v>2</v>
@@ -13676,22 +13688,22 @@
         <v>2.6</v>
       </c>
       <c r="AN61">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO61">
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR61">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AS61">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AT61">
         <v>3.27</v>
@@ -13810,7 +13822,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -13882,25 +13894,25 @@
         <v>1.71</v>
       </c>
       <c r="AN62">
-        <v>1.14</v>
+        <v>0.33</v>
       </c>
       <c r="AO62">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ62">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AS62">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AT62">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AU62">
         <v>7</v>
@@ -14088,25 +14100,25 @@
         <v>1.94</v>
       </c>
       <c r="AN63">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AO63">
-        <v>1.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP63">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ63">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR63">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="AS63">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT63">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="AU63">
         <v>3</v>
@@ -14297,22 +14309,22 @@
         <v>1</v>
       </c>
       <c r="AO64">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP64">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AQ64">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR64">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AS64">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="AT64">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AU64">
         <v>6</v>
@@ -14500,25 +14512,25 @@
         <v>1.95</v>
       </c>
       <c r="AN65">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AO65">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR65">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AS65">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AT65">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14706,25 +14718,25 @@
         <v>1.25</v>
       </c>
       <c r="AN66">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="AO66">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AP66">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ66">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR66">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AS66">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AT66">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="AU66">
         <v>3</v>
@@ -14840,7 +14852,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -14912,25 +14924,25 @@
         <v>1.4</v>
       </c>
       <c r="AN67">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AO67">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ67">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR67">
-        <v>1.18</v>
+        <v>0.97</v>
       </c>
       <c r="AS67">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT67">
-        <v>2.78</v>
+        <v>2.47</v>
       </c>
       <c r="AU67">
         <v>5</v>
@@ -15118,25 +15130,25 @@
         <v>1.25</v>
       </c>
       <c r="AN68">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO68">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ68">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR68">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AS68">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AT68">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="AU68">
         <v>6</v>
@@ -15252,7 +15264,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15324,25 +15336,25 @@
         <v>1.57</v>
       </c>
       <c r="AN69">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AO69">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ69">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR69">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AS69">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="AT69">
-        <v>3.59</v>
+        <v>3.32</v>
       </c>
       <c r="AU69">
         <v>6</v>
@@ -15458,7 +15470,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15530,25 +15542,25 @@
         <v>1.5</v>
       </c>
       <c r="AN70">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO70">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ70">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR70">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AS70">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AT70">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AU70">
         <v>3</v>
@@ -15664,7 +15676,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15736,25 +15748,25 @@
         <v>1.78</v>
       </c>
       <c r="AN71">
+        <v>1</v>
+      </c>
+      <c r="AO71">
+        <v>1.8</v>
+      </c>
+      <c r="AP71">
+        <v>1.7</v>
+      </c>
+      <c r="AQ71">
+        <v>1.55</v>
+      </c>
+      <c r="AR71">
+        <v>1.35</v>
+      </c>
+      <c r="AS71">
         <v>1.13</v>
       </c>
-      <c r="AO71">
-        <v>2.25</v>
-      </c>
-      <c r="AP71">
-        <v>1.38</v>
-      </c>
-      <c r="AQ71">
-        <v>1.76</v>
-      </c>
-      <c r="AR71">
-        <v>1.37</v>
-      </c>
-      <c r="AS71">
-        <v>1.22</v>
-      </c>
       <c r="AT71">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="AU71">
         <v>4</v>
@@ -15870,7 +15882,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -15942,25 +15954,25 @@
         <v>1.8</v>
       </c>
       <c r="AN72">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AO72">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR72">
-        <v>1.34</v>
+        <v>1.78</v>
       </c>
       <c r="AS72">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT72">
-        <v>2.57</v>
+        <v>2.91</v>
       </c>
       <c r="AU72">
         <v>8</v>
@@ -16148,25 +16160,25 @@
         <v>1.62</v>
       </c>
       <c r="AN73">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO73">
-        <v>1.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP73">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ73">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR73">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AS73">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AT73">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16354,25 +16366,25 @@
         <v>1.25</v>
       </c>
       <c r="AN74">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AO74">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ74">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR74">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS74">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AT74">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="AU74">
         <v>2</v>
@@ -16488,7 +16500,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16560,25 +16572,25 @@
         <v>2.45</v>
       </c>
       <c r="AN75">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AO75">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AP75">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ75">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR75">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AS75">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AT75">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="AU75">
         <v>5</v>
@@ -16694,7 +16706,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16766,25 +16778,25 @@
         <v>1.62</v>
       </c>
       <c r="AN76">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO76">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ76">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR76">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AS76">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AT76">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -16900,7 +16912,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -16972,25 +16984,25 @@
         <v>1.53</v>
       </c>
       <c r="AN77">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO77">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AP77">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ77">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR77">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AS77">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AT77">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AU77">
         <v>5</v>
@@ -17178,25 +17190,25 @@
         <v>1.71</v>
       </c>
       <c r="AN78">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AO78">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="AP78">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ78">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AS78">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AT78">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="AU78">
         <v>9</v>
@@ -17312,7 +17324,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17384,25 +17396,25 @@
         <v>1.22</v>
       </c>
       <c r="AN79">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AO79">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP79">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ79">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR79">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AS79">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AT79">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AU79">
         <v>3</v>
@@ -17590,25 +17602,25 @@
         <v>1.57</v>
       </c>
       <c r="AN80">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO80">
-        <v>1.3</v>
+        <v>0.25</v>
       </c>
       <c r="AP80">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ80">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR80">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AS80">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT80">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AU80">
         <v>10</v>
@@ -17724,7 +17736,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17796,25 +17808,25 @@
         <v>1.9</v>
       </c>
       <c r="AN81">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AO81">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ81">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR81">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AS81">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AT81">
-        <v>2.58</v>
+        <v>2.29</v>
       </c>
       <c r="AU81">
         <v>3</v>
@@ -18002,25 +18014,25 @@
         <v>1.3</v>
       </c>
       <c r="AN82">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO82">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ82">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR82">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AS82">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AT82">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AU82">
         <v>2</v>
@@ -18136,7 +18148,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18211,22 +18223,22 @@
         <v>1.67</v>
       </c>
       <c r="AO83">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ83">
+        <v>1</v>
+      </c>
+      <c r="AR83">
+        <v>1.79</v>
+      </c>
+      <c r="AS83">
         <v>1.19</v>
       </c>
-      <c r="AR83">
-        <v>1.74</v>
-      </c>
-      <c r="AS83">
-        <v>1.47</v>
-      </c>
       <c r="AT83">
-        <v>3.21</v>
+        <v>2.98</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18414,25 +18426,25 @@
         <v>1.95</v>
       </c>
       <c r="AN84">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AO84">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AP84">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ84">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR84">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS84">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AT84">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AU84">
         <v>2</v>
@@ -18620,25 +18632,25 @@
         <v>1.25</v>
       </c>
       <c r="AN85">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AO85">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ85">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR85">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AS85">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AT85">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AU85">
         <v>5</v>
@@ -18754,7 +18766,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -18826,25 +18838,25 @@
         <v>1.44</v>
       </c>
       <c r="AN86">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AO86">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="AP86">
+        <v>1.64</v>
+      </c>
+      <c r="AQ86">
+        <v>1.73</v>
+      </c>
+      <c r="AR86">
+        <v>1.56</v>
+      </c>
+      <c r="AS86">
         <v>1.43</v>
       </c>
-      <c r="AQ86">
-        <v>1.76</v>
-      </c>
-      <c r="AR86">
-        <v>1.65</v>
-      </c>
-      <c r="AS86">
-        <v>1.74</v>
-      </c>
       <c r="AT86">
-        <v>3.39</v>
+        <v>2.99</v>
       </c>
       <c r="AU86">
         <v>6</v>
@@ -19032,25 +19044,25 @@
         <v>2.9</v>
       </c>
       <c r="AN87">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ87">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR87">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AS87">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AT87">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AU87">
         <v>8</v>
@@ -19238,25 +19250,25 @@
         <v>1.52</v>
       </c>
       <c r="AN88">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AO88">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AP88">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ88">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR88">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AS88">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT88">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="AU88">
         <v>5</v>
@@ -19444,22 +19456,22 @@
         <v>1.86</v>
       </c>
       <c r="AN89">
+        <v>1.5</v>
+      </c>
+      <c r="AO89">
+        <v>0.67</v>
+      </c>
+      <c r="AP89">
+        <v>1.4</v>
+      </c>
+      <c r="AQ89">
+        <v>1.4</v>
+      </c>
+      <c r="AR89">
+        <v>1.6</v>
+      </c>
+      <c r="AS89">
         <v>1.09</v>
-      </c>
-      <c r="AO89">
-        <v>1.55</v>
-      </c>
-      <c r="AP89">
-        <v>1.14</v>
-      </c>
-      <c r="AQ89">
-        <v>1.71</v>
-      </c>
-      <c r="AR89">
-        <v>1.53</v>
-      </c>
-      <c r="AS89">
-        <v>1.16</v>
       </c>
       <c r="AT89">
         <v>2.69</v>
@@ -19578,7 +19590,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19650,25 +19662,25 @@
         <v>1.24</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AO90">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AP90">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ90">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR90">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS90">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AT90">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AU90">
         <v>4</v>
@@ -19784,7 +19796,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -19856,25 +19868,25 @@
         <v>2.7</v>
       </c>
       <c r="AN91">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AO91">
-        <v>1.27</v>
+        <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ91">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR91">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AS91">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AT91">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -19990,7 +20002,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20062,25 +20074,25 @@
         <v>1.37</v>
       </c>
       <c r="AN92">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO92">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ92">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR92">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AS92">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AT92">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AU92">
         <v>3</v>
@@ -20196,7 +20208,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20268,25 +20280,25 @@
         <v>1.44</v>
       </c>
       <c r="AN93">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="AO93">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP93">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ93">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR93">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AS93">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AT93">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU93">
         <v>3</v>
@@ -20474,25 +20486,25 @@
         <v>1.29</v>
       </c>
       <c r="AN94">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AO94">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ94">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR94">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AS94">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AT94">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="AU94">
         <v>8</v>
@@ -20608,7 +20620,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20680,25 +20692,25 @@
         <v>3.15</v>
       </c>
       <c r="AN95">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AO95">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP95">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ95">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR95">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AS95">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AT95">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="AU95">
         <v>9</v>
@@ -20886,25 +20898,25 @@
         <v>1.42</v>
       </c>
       <c r="AN96">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AO96">
-        <v>1.08</v>
+        <v>0.2</v>
       </c>
       <c r="AP96">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR96">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AS96">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AT96">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="AU96">
         <v>9</v>
@@ -21092,25 +21104,25 @@
         <v>1.78</v>
       </c>
       <c r="AN97">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AO97">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AP97">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ97">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR97">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AS97">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT97">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AU97">
         <v>5</v>
@@ -21301,22 +21313,22 @@
         <v>1.17</v>
       </c>
       <c r="AO98">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AQ98">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR98">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AS98">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AT98">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AU98">
         <v>6</v>
@@ -21504,25 +21516,25 @@
         <v>1.15</v>
       </c>
       <c r="AN99">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO99">
+        <v>1.67</v>
+      </c>
+      <c r="AP99">
         <v>1.64</v>
       </c>
-      <c r="AP99">
-        <v>1.48</v>
-      </c>
       <c r="AQ99">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR99">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AS99">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AT99">
-        <v>3.07</v>
+        <v>2.86</v>
       </c>
       <c r="AU99">
         <v>0</v>
@@ -21710,25 +21722,25 @@
         <v>2.85</v>
       </c>
       <c r="AN100">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AO100">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP100">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ100">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR100">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AS100">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AT100">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21844,7 +21856,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21916,25 +21928,25 @@
         <v>1.2</v>
       </c>
       <c r="AN101">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AO101">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ101">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR101">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AS101">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AT101">
-        <v>2.91</v>
+        <v>2.58</v>
       </c>
       <c r="AU101">
         <v>2</v>
@@ -22122,25 +22134,25 @@
         <v>1.87</v>
       </c>
       <c r="AN102">
+        <v>1.67</v>
+      </c>
+      <c r="AO102">
         <v>1.17</v>
       </c>
-      <c r="AO102">
-        <v>1</v>
-      </c>
       <c r="AP102">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ102">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR102">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AS102">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT102">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU102">
         <v>4</v>
@@ -22328,25 +22340,25 @@
         <v>1.72</v>
       </c>
       <c r="AN103">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AO103">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="AP103">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ103">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR103">
+        <v>1.37</v>
+      </c>
+      <c r="AS103">
         <v>1.44</v>
       </c>
-      <c r="AS103">
-        <v>1.56</v>
-      </c>
       <c r="AT103">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22462,7 +22474,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22534,25 +22546,25 @@
         <v>1.95</v>
       </c>
       <c r="AN104">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AO104">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR104">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AS104">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AT104">
-        <v>3.31</v>
+        <v>3.52</v>
       </c>
       <c r="AU104">
         <v>9</v>
@@ -22740,25 +22752,25 @@
         <v>1.95</v>
       </c>
       <c r="AN105">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AO105">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ105">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR105">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AS105">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AT105">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU105">
         <v>6</v>
@@ -22946,25 +22958,25 @@
         <v>1.66</v>
       </c>
       <c r="AN106">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AO106">
-        <v>1.31</v>
+        <v>0.67</v>
       </c>
       <c r="AP106">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ106">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR106">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AS106">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AT106">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AU106">
         <v>11</v>
@@ -23080,7 +23092,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23152,25 +23164,25 @@
         <v>1.55</v>
       </c>
       <c r="AN107">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AO107">
-        <v>1.38</v>
+        <v>0.71</v>
       </c>
       <c r="AP107">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ107">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR107">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AS107">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AT107">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AU107">
         <v>4</v>
@@ -23286,7 +23298,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23358,25 +23370,25 @@
         <v>1.97</v>
       </c>
       <c r="AN108">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AO108">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ108">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR108">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AS108">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AT108">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="AU108">
         <v>0</v>
@@ -23564,25 +23576,25 @@
         <v>2</v>
       </c>
       <c r="AN109">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AO109">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ109">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR109">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AS109">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AT109">
-        <v>3.21</v>
+        <v>3.51</v>
       </c>
       <c r="AU109">
         <v>7</v>
@@ -23698,7 +23710,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23770,25 +23782,25 @@
         <v>1.32</v>
       </c>
       <c r="AN110">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO110">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ110">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR110">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AS110">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AT110">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="AU110">
         <v>3</v>
@@ -23904,7 +23916,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -23976,25 +23988,25 @@
         <v>1.34</v>
       </c>
       <c r="AN111">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO111">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AP111">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ111">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR111">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AS111">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AT111">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AU111">
         <v>5</v>
@@ -24110,7 +24122,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24182,25 +24194,25 @@
         <v>1.08</v>
       </c>
       <c r="AN112">
-        <v>0.93</v>
+        <v>1.33</v>
       </c>
       <c r="AO112">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR112">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AS112">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="AT112">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="AU112">
         <v>3</v>
@@ -24316,7 +24328,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24388,25 +24400,25 @@
         <v>1.8</v>
       </c>
       <c r="AN113">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AO113">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AP113">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AQ113">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR113">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AS113">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT113">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU113">
         <v>5</v>
@@ -24594,25 +24606,25 @@
         <v>1.8</v>
       </c>
       <c r="AN114">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="AO114">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AP114">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR114">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AS114">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AT114">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="AU114">
         <v>4</v>
@@ -24728,7 +24740,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -24800,25 +24812,25 @@
         <v>1.42</v>
       </c>
       <c r="AN115">
-        <v>1.21</v>
+        <v>1.86</v>
       </c>
       <c r="AO115">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AP115">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ115">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR115">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AS115">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT115">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AU115">
         <v>7</v>
@@ -25006,25 +25018,25 @@
         <v>1.9</v>
       </c>
       <c r="AN116">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AO116">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ116">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR116">
+        <v>1.34</v>
+      </c>
+      <c r="AS116">
         <v>1.3</v>
       </c>
-      <c r="AS116">
-        <v>1.46</v>
-      </c>
       <c r="AT116">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU116">
         <v>4</v>
@@ -25140,7 +25152,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25212,25 +25224,25 @@
         <v>1.62</v>
       </c>
       <c r="AN117">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO117">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ117">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR117">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AS117">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AT117">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AU117">
         <v>4</v>
@@ -25418,25 +25430,25 @@
         <v>1.5</v>
       </c>
       <c r="AN118">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="AO118">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="AP118">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ118">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR118">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AS118">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AT118">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AU118">
         <v>7</v>
@@ -25624,25 +25636,25 @@
         <v>2.2</v>
       </c>
       <c r="AN119">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AO119">
-        <v>0.93</v>
+        <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ119">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR119">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AS119">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AT119">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="AU119">
         <v>5</v>
@@ -25830,25 +25842,25 @@
         <v>1.76</v>
       </c>
       <c r="AN120">
+        <v>1.5</v>
+      </c>
+      <c r="AO120">
+        <v>0.63</v>
+      </c>
+      <c r="AP120">
+        <v>1.09</v>
+      </c>
+      <c r="AQ120">
+        <v>0.55</v>
+      </c>
+      <c r="AR120">
         <v>1.36</v>
       </c>
-      <c r="AO120">
-        <v>0.86</v>
-      </c>
-      <c r="AP120">
-        <v>1.14</v>
-      </c>
-      <c r="AQ120">
-        <v>0.86</v>
-      </c>
-      <c r="AR120">
-        <v>1.32</v>
-      </c>
       <c r="AS120">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AT120">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU120">
         <v>2</v>
@@ -25964,7 +25976,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26036,25 +26048,25 @@
         <v>1.36</v>
       </c>
       <c r="AN121">
-        <v>1.6</v>
+        <v>2.29</v>
       </c>
       <c r="AO121">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AP121">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR121">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AS121">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="AT121">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AU121">
         <v>5</v>
@@ -26170,7 +26182,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26242,25 +26254,25 @@
         <v>1.36</v>
       </c>
       <c r="AN122">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO122">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ122">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR122">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AS122">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AT122">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="AU122">
         <v>3</v>
@@ -26448,25 +26460,25 @@
         <v>2.2</v>
       </c>
       <c r="AN123">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AO123">
-        <v>0.87</v>
+        <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ123">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR123">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AS123">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT123">
-        <v>3.01</v>
+        <v>3.27</v>
       </c>
       <c r="AU123">
         <v>8</v>
@@ -26654,25 +26666,25 @@
         <v>1.99</v>
       </c>
       <c r="AN124">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO124">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AP124">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ124">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR124">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AS124">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AT124">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AU124">
         <v>13</v>
@@ -26788,7 +26800,7 @@
         <v>86</v>
       </c>
       <c r="P125" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q125">
         <v>3.3</v>
@@ -26860,25 +26872,25 @@
         <v>1.44</v>
       </c>
       <c r="AN125">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AO125">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="AP125">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ125">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR125">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AS125">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AT125">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AU125">
         <v>6</v>
@@ -26994,7 +27006,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27066,25 +27078,25 @@
         <v>1.41</v>
       </c>
       <c r="AN126">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO126">
         <v>1.5</v>
       </c>
       <c r="AP126">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ126">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR126">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS126">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AT126">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AU126">
         <v>7</v>
@@ -27272,25 +27284,25 @@
         <v>1.36</v>
       </c>
       <c r="AN127">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="AO127">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AP127">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR127">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AS127">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AT127">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="AU127">
         <v>7</v>
@@ -27478,25 +27490,25 @@
         <v>1.33</v>
       </c>
       <c r="AN128">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO128">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ128">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR128">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS128">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AT128">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="AU128">
         <v>3</v>
@@ -27684,25 +27696,25 @@
         <v>1.17</v>
       </c>
       <c r="AN129">
-        <v>0.87</v>
+        <v>1.17</v>
       </c>
       <c r="AO129">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ129">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR129">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AS129">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AT129">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="AU129">
         <v>5</v>
@@ -27893,22 +27905,22 @@
         <v>1.38</v>
       </c>
       <c r="AO130">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="AP130">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AQ130">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR130">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AS130">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AT130">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU130">
         <v>6</v>
@@ -28024,7 +28036,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28096,25 +28108,25 @@
         <v>1.56</v>
       </c>
       <c r="AN131">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO131">
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ131">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR131">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AS131">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AT131">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="AU131">
         <v>0</v>
@@ -28230,7 +28242,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28302,25 +28314,25 @@
         <v>1.28</v>
       </c>
       <c r="AN132">
-        <v>0.8100000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AP132">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ132">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AR132">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AS132">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AT132">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="AU132">
         <v>5</v>
@@ -28436,7 +28448,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28508,25 +28520,25 @@
         <v>1.7</v>
       </c>
       <c r="AN133">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AO133">
+        <v>1.25</v>
+      </c>
+      <c r="AP133">
+        <v>1.64</v>
+      </c>
+      <c r="AQ133">
+        <v>1.09</v>
+      </c>
+      <c r="AR133">
+        <v>1.85</v>
+      </c>
+      <c r="AS133">
         <v>1.44</v>
       </c>
-      <c r="AP133">
-        <v>1.67</v>
-      </c>
-      <c r="AQ133">
-        <v>1.38</v>
-      </c>
-      <c r="AR133">
-        <v>1.6</v>
-      </c>
-      <c r="AS133">
-        <v>1.49</v>
-      </c>
       <c r="AT133">
-        <v>3.09</v>
+        <v>3.29</v>
       </c>
       <c r="AU133">
         <v>3</v>
@@ -28717,22 +28729,22 @@
         <v>1.5</v>
       </c>
       <c r="AO134">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AP134">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ134">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR134">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AS134">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AT134">
-        <v>3.09</v>
+        <v>3.33</v>
       </c>
       <c r="AU134">
         <v>8</v>
@@ -28920,25 +28932,25 @@
         <v>1.62</v>
       </c>
       <c r="AN135">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO135">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP135">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR135">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS135">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AT135">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AU135">
         <v>4</v>
@@ -29054,7 +29066,7 @@
         <v>99</v>
       </c>
       <c r="P136" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29126,25 +29138,25 @@
         <v>1.46</v>
       </c>
       <c r="AN136">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AO136">
-        <v>1.25</v>
+        <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ136">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR136">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AS136">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AT136">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="AU136">
         <v>4</v>
@@ -29260,7 +29272,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29332,25 +29344,25 @@
         <v>1.25</v>
       </c>
       <c r="AN137">
+        <v>1.5</v>
+      </c>
+      <c r="AO137">
         <v>1.13</v>
       </c>
-      <c r="AO137">
-        <v>1.56</v>
-      </c>
       <c r="AP137">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ137">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR137">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AS137">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT137">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AU137">
         <v>6</v>
@@ -29538,25 +29550,25 @@
         <v>1.34</v>
       </c>
       <c r="AN138">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AO138">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ138">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR138">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AS138">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT138">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="AU138">
         <v>4</v>
@@ -29744,25 +29756,25 @@
         <v>1.72</v>
       </c>
       <c r="AN139">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AO139">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ139">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR139">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AS139">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AT139">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="AU139">
         <v>6</v>
@@ -29878,7 +29890,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -29950,25 +29962,25 @@
         <v>1.37</v>
       </c>
       <c r="AN140">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AO140">
-        <v>0.9399999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="AP140">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ140">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR140">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AS140">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT140">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="AU140">
         <v>7</v>
@@ -30156,25 +30168,25 @@
         <v>1.42</v>
       </c>
       <c r="AN141">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AO141">
-        <v>1.24</v>
+        <v>0.63</v>
       </c>
       <c r="AP141">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR141">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AS141">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AT141">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AU141">
         <v>7</v>
@@ -30290,7 +30302,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30362,25 +30374,25 @@
         <v>1.47</v>
       </c>
       <c r="AN142">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AO142">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ142">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR142">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AS142">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AT142">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AU142">
         <v>4</v>
@@ -30496,7 +30508,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30568,25 +30580,25 @@
         <v>1.42</v>
       </c>
       <c r="AN143">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AO143">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ143">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR143">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AS143">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AT143">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AU143">
         <v>6</v>
@@ -30702,7 +30714,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30774,25 +30786,25 @@
         <v>1.83</v>
       </c>
       <c r="AN144">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AO144">
-        <v>1.06</v>
+        <v>0.75</v>
       </c>
       <c r="AP144">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ144">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR144">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AS144">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AT144">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="AU144">
         <v>8</v>
@@ -30908,7 +30920,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -30980,25 +30992,25 @@
         <v>1.21</v>
       </c>
       <c r="AN145">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AO145">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ145">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR145">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AS145">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AT145">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AU145">
         <v>4</v>
@@ -31186,25 +31198,25 @@
         <v>1.41</v>
       </c>
       <c r="AN146">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AO146">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AP146">
+        <v>1.64</v>
+      </c>
+      <c r="AQ146">
+        <v>1.09</v>
+      </c>
+      <c r="AR146">
+        <v>1.46</v>
+      </c>
+      <c r="AS146">
         <v>1.43</v>
       </c>
-      <c r="AQ146">
-        <v>1.38</v>
-      </c>
-      <c r="AR146">
-        <v>1.49</v>
-      </c>
-      <c r="AS146">
-        <v>1.49</v>
-      </c>
       <c r="AT146">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="AU146">
         <v>5</v>
@@ -31320,7 +31332,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31392,25 +31404,25 @@
         <v>1.32</v>
       </c>
       <c r="AN147">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO147">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AP147">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ147">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AR147">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AS147">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AT147">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AU147">
         <v>4</v>
@@ -31526,7 +31538,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31598,25 +31610,25 @@
         <v>1.27</v>
       </c>
       <c r="AN148">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AO148">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ148">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR148">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AS148">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT148">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AU148">
         <v>4</v>
@@ -31732,7 +31744,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31804,25 +31816,25 @@
         <v>1.64</v>
       </c>
       <c r="AN149">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO149">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP149">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ149">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR149">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AS149">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AT149">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="AU149">
         <v>7</v>
@@ -31938,7 +31950,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32010,25 +32022,25 @@
         <v>1.42</v>
       </c>
       <c r="AN150">
-        <v>1.17</v>
+        <v>1.78</v>
       </c>
       <c r="AO150">
-        <v>1.17</v>
+        <v>0.89</v>
       </c>
       <c r="AP150">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ150">
-        <v>1.14</v>
+        <v>0.91</v>
       </c>
       <c r="AR150">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AS150">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT150">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AU150">
         <v>5</v>
@@ -32219,22 +32231,22 @@
         <v>1.67</v>
       </c>
       <c r="AO151">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP151">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AQ151">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR151">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AS151">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AT151">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AU151">
         <v>9</v>
@@ -32422,25 +32434,25 @@
         <v>1.38</v>
       </c>
       <c r="AN152">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="AO152">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AP152">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AQ152">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR152">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AS152">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AT152">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AU152">
         <v>5</v>
@@ -32556,7 +32568,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32628,25 +32640,25 @@
         <v>1.35</v>
       </c>
       <c r="AN153">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AO153">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AP153">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ153">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR153">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AS153">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="AT153">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AU153">
         <v>6</v>
@@ -32762,7 +32774,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -32834,25 +32846,25 @@
         <v>1.44</v>
       </c>
       <c r="AN154">
-        <v>0.95</v>
+        <v>1.33</v>
       </c>
       <c r="AO154">
-        <v>1.16</v>
+        <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AQ154">
-        <v>1.24</v>
+        <v>0.73</v>
       </c>
       <c r="AR154">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="AS154">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AT154">
-        <v>2.67</v>
+        <v>2.99</v>
       </c>
       <c r="AU154">
         <v>5</v>
@@ -33040,25 +33052,25 @@
         <v>1.78</v>
       </c>
       <c r="AN155">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AO155">
-        <v>1.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP155">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
-        <v>1.05</v>
+        <v>0.5</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
       </c>
       <c r="AS155">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT155">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AU155">
         <v>8</v>
@@ -33246,25 +33258,25 @@
         <v>1.66</v>
       </c>
       <c r="AN156">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AO156">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AQ156">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AR156">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AS156">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AT156">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AU156">
         <v>4</v>
@@ -33380,7 +33392,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33452,25 +33464,25 @@
         <v>1.68</v>
       </c>
       <c r="AN157">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AO157">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AQ157">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AR157">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AS157">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AT157">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="AU157">
         <v>7</v>
@@ -33586,7 +33598,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -33658,25 +33670,25 @@
         <v>1.65</v>
       </c>
       <c r="AN158">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AO158">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AP158">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AQ158">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AR158">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AS158">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AT158">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="AU158">
         <v>7</v>
@@ -33864,25 +33876,25 @@
         <v>1.17</v>
       </c>
       <c r="AN159">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AO159">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AP159">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AQ159">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AR159">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AS159">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AT159">
-        <v>2.91</v>
+        <v>2.68</v>
       </c>
       <c r="AU159">
         <v>3</v>
@@ -34070,25 +34082,25 @@
         <v>1.27</v>
       </c>
       <c r="AN160">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="AO160">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AQ160">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR160">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AS160">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AT160">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="AU160">
         <v>7</v>
@@ -34276,25 +34288,25 @@
         <v>2.29</v>
       </c>
       <c r="AN161">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AO161">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP161">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AQ161">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="AR161">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AS161">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AT161">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34482,25 +34494,25 @@
         <v>1.43</v>
       </c>
       <c r="AN162">
+        <v>1.7</v>
+      </c>
+      <c r="AO162">
+        <v>1.6</v>
+      </c>
+      <c r="AP162">
+        <v>1.64</v>
+      </c>
+      <c r="AQ162">
+        <v>1.55</v>
+      </c>
+      <c r="AR162">
         <v>1.45</v>
       </c>
-      <c r="AO162">
-        <v>1.8</v>
-      </c>
-      <c r="AP162">
-        <v>1.43</v>
-      </c>
-      <c r="AQ162">
-        <v>1.76</v>
-      </c>
-      <c r="AR162">
-        <v>1.47</v>
-      </c>
       <c r="AS162">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT162">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AU162">
         <v>0</v>
@@ -34688,25 +34700,25 @@
         <v>1.55</v>
       </c>
       <c r="AN163">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO163">
-        <v>1.15</v>
+        <v>0.9</v>
       </c>
       <c r="AP163">
+        <v>1.73</v>
+      </c>
+      <c r="AQ163">
+        <v>0.91</v>
+      </c>
+      <c r="AR163">
         <v>1.24</v>
       </c>
-      <c r="AQ163">
-        <v>1.14</v>
-      </c>
-      <c r="AR163">
-        <v>1.28</v>
-      </c>
       <c r="AS163">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AT163">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="AU163">
         <v>3</v>
@@ -34822,7 +34834,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -34894,25 +34906,25 @@
         <v>1.16</v>
       </c>
       <c r="AN164">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AO164">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AP164">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="AQ164">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AR164">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AS164">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AT164">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="AU164">
         <v>5</v>
@@ -35100,25 +35112,25 @@
         <v>1.8</v>
       </c>
       <c r="AN165">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO165">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AP165">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ165">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AR165">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS165">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AT165">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU165">
         <v>8</v>
@@ -35234,7 +35246,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35306,25 +35318,25 @@
         <v>1.94</v>
       </c>
       <c r="AN166">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO166">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AP166">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AQ166">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AR166">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AS166">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AT166">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="AU166">
         <v>5</v>
@@ -35512,25 +35524,25 @@
         <v>1.37</v>
       </c>
       <c r="AN167">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AO167">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AP167">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AQ167">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AR167">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AS167">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AT167">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU167">
         <v>5</v>
@@ -35718,25 +35730,25 @@
         <v>1.59</v>
       </c>
       <c r="AN168">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AO168">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AP168">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AQ168">
-        <v>0.86</v>
+        <v>0.55</v>
       </c>
       <c r="AR168">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AS168">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AT168">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AU168">
         <v>7</v>
@@ -35852,7 +35864,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -35924,25 +35936,25 @@
         <v>1.19</v>
       </c>
       <c r="AN169">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="AO169">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AP169">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="AQ169">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AR169">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AS169">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AT169">
-        <v>3.19</v>
+        <v>2.98</v>
       </c>
       <c r="AU169">
         <v>0</v>
@@ -36009,6 +36021,830 @@
       </c>
       <c r="BP169">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7486663</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45674.5</v>
+      </c>
+      <c r="F170">
+        <v>22</v>
+      </c>
+      <c r="G170" t="s">
+        <v>79</v>
+      </c>
+      <c r="H170" t="s">
+        <v>72</v>
+      </c>
+      <c r="I170">
+        <v>2</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>2</v>
+      </c>
+      <c r="L170">
+        <v>3</v>
+      </c>
+      <c r="M170">
+        <v>2</v>
+      </c>
+      <c r="N170">
+        <v>5</v>
+      </c>
+      <c r="O170" t="s">
+        <v>193</v>
+      </c>
+      <c r="P170" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q170">
+        <v>3.9</v>
+      </c>
+      <c r="R170">
+        <v>1.98</v>
+      </c>
+      <c r="S170">
+        <v>2.95</v>
+      </c>
+      <c r="T170">
+        <v>1.49</v>
+      </c>
+      <c r="U170">
+        <v>2.45</v>
+      </c>
+      <c r="V170">
+        <v>3.2</v>
+      </c>
+      <c r="W170">
+        <v>1.3</v>
+      </c>
+      <c r="X170">
+        <v>9</v>
+      </c>
+      <c r="Y170">
+        <v>1.04</v>
+      </c>
+      <c r="Z170">
+        <v>3.25</v>
+      </c>
+      <c r="AA170">
+        <v>3.1</v>
+      </c>
+      <c r="AB170">
+        <v>2.24</v>
+      </c>
+      <c r="AC170">
+        <v>1.08</v>
+      </c>
+      <c r="AD170">
+        <v>7</v>
+      </c>
+      <c r="AE170">
+        <v>1.39</v>
+      </c>
+      <c r="AF170">
+        <v>2.85</v>
+      </c>
+      <c r="AG170">
+        <v>2.1</v>
+      </c>
+      <c r="AH170">
+        <v>1.65</v>
+      </c>
+      <c r="AI170">
+        <v>1.94</v>
+      </c>
+      <c r="AJ170">
+        <v>1.81</v>
+      </c>
+      <c r="AK170">
+        <v>1.54</v>
+      </c>
+      <c r="AL170">
+        <v>1.32</v>
+      </c>
+      <c r="AM170">
+        <v>1.3</v>
+      </c>
+      <c r="AN170">
+        <v>0.9</v>
+      </c>
+      <c r="AO170">
+        <v>1.2</v>
+      </c>
+      <c r="AP170">
+        <v>1.09</v>
+      </c>
+      <c r="AQ170">
+        <v>1.09</v>
+      </c>
+      <c r="AR170">
+        <v>1.38</v>
+      </c>
+      <c r="AS170">
+        <v>1.48</v>
+      </c>
+      <c r="AT170">
+        <v>2.86</v>
+      </c>
+      <c r="AU170">
+        <v>5</v>
+      </c>
+      <c r="AV170">
+        <v>6</v>
+      </c>
+      <c r="AW170">
+        <v>7</v>
+      </c>
+      <c r="AX170">
+        <v>17</v>
+      </c>
+      <c r="AY170">
+        <v>12</v>
+      </c>
+      <c r="AZ170">
+        <v>26</v>
+      </c>
+      <c r="BA170">
+        <v>5</v>
+      </c>
+      <c r="BB170">
+        <v>8</v>
+      </c>
+      <c r="BC170">
+        <v>13</v>
+      </c>
+      <c r="BD170">
+        <v>2.23</v>
+      </c>
+      <c r="BE170">
+        <v>6.4</v>
+      </c>
+      <c r="BF170">
+        <v>1.79</v>
+      </c>
+      <c r="BG170">
+        <v>1.36</v>
+      </c>
+      <c r="BH170">
+        <v>2.8</v>
+      </c>
+      <c r="BI170">
+        <v>1.62</v>
+      </c>
+      <c r="BJ170">
+        <v>2.1</v>
+      </c>
+      <c r="BK170">
+        <v>2.02</v>
+      </c>
+      <c r="BL170">
+        <v>1.67</v>
+      </c>
+      <c r="BM170">
+        <v>2.6</v>
+      </c>
+      <c r="BN170">
+        <v>1.41</v>
+      </c>
+      <c r="BO170">
+        <v>3.4</v>
+      </c>
+      <c r="BP170">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7486668</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45674.625</v>
+      </c>
+      <c r="F171">
+        <v>22</v>
+      </c>
+      <c r="G171" t="s">
+        <v>74</v>
+      </c>
+      <c r="H171" t="s">
+        <v>71</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>2</v>
+      </c>
+      <c r="O171" t="s">
+        <v>98</v>
+      </c>
+      <c r="P171" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q171">
+        <v>1.99</v>
+      </c>
+      <c r="R171">
+        <v>2.21</v>
+      </c>
+      <c r="S171">
+        <v>6.8</v>
+      </c>
+      <c r="T171">
+        <v>1.44</v>
+      </c>
+      <c r="U171">
+        <v>2.6</v>
+      </c>
+      <c r="V171">
+        <v>2.88</v>
+      </c>
+      <c r="W171">
+        <v>1.36</v>
+      </c>
+      <c r="X171">
+        <v>7.4</v>
+      </c>
+      <c r="Y171">
+        <v>1.07</v>
+      </c>
+      <c r="Z171">
+        <v>1.44</v>
+      </c>
+      <c r="AA171">
+        <v>4.2</v>
+      </c>
+      <c r="AB171">
+        <v>6.8</v>
+      </c>
+      <c r="AC171">
+        <v>1.05</v>
+      </c>
+      <c r="AD171">
+        <v>8.5</v>
+      </c>
+      <c r="AE171">
+        <v>1.32</v>
+      </c>
+      <c r="AF171">
+        <v>3.2</v>
+      </c>
+      <c r="AG171">
+        <v>1.97</v>
+      </c>
+      <c r="AH171">
+        <v>1.78</v>
+      </c>
+      <c r="AI171">
+        <v>2.1</v>
+      </c>
+      <c r="AJ171">
+        <v>1.62</v>
+      </c>
+      <c r="AK171">
+        <v>1.09</v>
+      </c>
+      <c r="AL171">
+        <v>1.19</v>
+      </c>
+      <c r="AM171">
+        <v>2.34</v>
+      </c>
+      <c r="AN171">
+        <v>1.8</v>
+      </c>
+      <c r="AO171">
+        <v>0.7</v>
+      </c>
+      <c r="AP171">
+        <v>1.73</v>
+      </c>
+      <c r="AQ171">
+        <v>0.73</v>
+      </c>
+      <c r="AR171">
+        <v>2.04</v>
+      </c>
+      <c r="AS171">
+        <v>1.33</v>
+      </c>
+      <c r="AT171">
+        <v>3.37</v>
+      </c>
+      <c r="AU171">
+        <v>9</v>
+      </c>
+      <c r="AV171">
+        <v>2</v>
+      </c>
+      <c r="AW171">
+        <v>18</v>
+      </c>
+      <c r="AX171">
+        <v>0</v>
+      </c>
+      <c r="AY171">
+        <v>33</v>
+      </c>
+      <c r="AZ171">
+        <v>2</v>
+      </c>
+      <c r="BA171">
+        <v>9</v>
+      </c>
+      <c r="BB171">
+        <v>2</v>
+      </c>
+      <c r="BC171">
+        <v>11</v>
+      </c>
+      <c r="BD171">
+        <v>1.36</v>
+      </c>
+      <c r="BE171">
+        <v>6.75</v>
+      </c>
+      <c r="BF171">
+        <v>3.55</v>
+      </c>
+      <c r="BG171">
+        <v>1.55</v>
+      </c>
+      <c r="BH171">
+        <v>2.25</v>
+      </c>
+      <c r="BI171">
+        <v>1.9</v>
+      </c>
+      <c r="BJ171">
+        <v>1.76</v>
+      </c>
+      <c r="BK171">
+        <v>2.43</v>
+      </c>
+      <c r="BL171">
+        <v>1.46</v>
+      </c>
+      <c r="BM171">
+        <v>3.2</v>
+      </c>
+      <c r="BN171">
+        <v>1.28</v>
+      </c>
+      <c r="BO171">
+        <v>4.35</v>
+      </c>
+      <c r="BP171">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7486665</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45675.39583333334</v>
+      </c>
+      <c r="F172">
+        <v>22</v>
+      </c>
+      <c r="G172" t="s">
+        <v>82</v>
+      </c>
+      <c r="H172" t="s">
+        <v>84</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="N172">
+        <v>3</v>
+      </c>
+      <c r="O172" t="s">
+        <v>194</v>
+      </c>
+      <c r="P172" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q172">
+        <v>2.14</v>
+      </c>
+      <c r="R172">
+        <v>2.16</v>
+      </c>
+      <c r="S172">
+        <v>5.8</v>
+      </c>
+      <c r="T172">
+        <v>1.46</v>
+      </c>
+      <c r="U172">
+        <v>2.55</v>
+      </c>
+      <c r="V172">
+        <v>2.94</v>
+      </c>
+      <c r="W172">
+        <v>1.37</v>
+      </c>
+      <c r="X172">
+        <v>7.5</v>
+      </c>
+      <c r="Y172">
+        <v>1.07</v>
+      </c>
+      <c r="Z172">
+        <v>1.44</v>
+      </c>
+      <c r="AA172">
+        <v>4.1</v>
+      </c>
+      <c r="AB172">
+        <v>6.3</v>
+      </c>
+      <c r="AC172">
+        <v>1.03</v>
+      </c>
+      <c r="AD172">
+        <v>9</v>
+      </c>
+      <c r="AE172">
+        <v>1.32</v>
+      </c>
+      <c r="AF172">
+        <v>3.2</v>
+      </c>
+      <c r="AG172">
+        <v>2.05</v>
+      </c>
+      <c r="AH172">
+        <v>1.83</v>
+      </c>
+      <c r="AI172">
+        <v>1.96</v>
+      </c>
+      <c r="AJ172">
+        <v>1.72</v>
+      </c>
+      <c r="AK172">
+        <v>1.13</v>
+      </c>
+      <c r="AL172">
+        <v>1.22</v>
+      </c>
+      <c r="AM172">
+        <v>2.08</v>
+      </c>
+      <c r="AN172">
+        <v>2</v>
+      </c>
+      <c r="AO172">
+        <v>0.5</v>
+      </c>
+      <c r="AP172">
+        <v>2.09</v>
+      </c>
+      <c r="AQ172">
+        <v>0.45</v>
+      </c>
+      <c r="AR172">
+        <v>1.54</v>
+      </c>
+      <c r="AS172">
+        <v>1.15</v>
+      </c>
+      <c r="AT172">
+        <v>2.69</v>
+      </c>
+      <c r="AU172">
+        <v>11</v>
+      </c>
+      <c r="AV172">
+        <v>3</v>
+      </c>
+      <c r="AW172">
+        <v>8</v>
+      </c>
+      <c r="AX172">
+        <v>3</v>
+      </c>
+      <c r="AY172">
+        <v>23</v>
+      </c>
+      <c r="AZ172">
+        <v>6</v>
+      </c>
+      <c r="BA172">
+        <v>7</v>
+      </c>
+      <c r="BB172">
+        <v>2</v>
+      </c>
+      <c r="BC172">
+        <v>9</v>
+      </c>
+      <c r="BD172">
+        <v>1.68</v>
+      </c>
+      <c r="BE172">
+        <v>6.25</v>
+      </c>
+      <c r="BF172">
+        <v>2.45</v>
+      </c>
+      <c r="BG172">
+        <v>1.52</v>
+      </c>
+      <c r="BH172">
+        <v>2.32</v>
+      </c>
+      <c r="BI172">
+        <v>1.86</v>
+      </c>
+      <c r="BJ172">
+        <v>1.8</v>
+      </c>
+      <c r="BK172">
+        <v>2.38</v>
+      </c>
+      <c r="BL172">
+        <v>1.48</v>
+      </c>
+      <c r="BM172">
+        <v>3.15</v>
+      </c>
+      <c r="BN172">
+        <v>1.29</v>
+      </c>
+      <c r="BO172">
+        <v>4.3</v>
+      </c>
+      <c r="BP172">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7486664</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45675.60416666666</v>
+      </c>
+      <c r="F173">
+        <v>22</v>
+      </c>
+      <c r="G173" t="s">
+        <v>85</v>
+      </c>
+      <c r="H173" t="s">
+        <v>77</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173" t="s">
+        <v>86</v>
+      </c>
+      <c r="P173" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q173">
+        <v>3.25</v>
+      </c>
+      <c r="R173">
+        <v>1.9</v>
+      </c>
+      <c r="S173">
+        <v>3.6</v>
+      </c>
+      <c r="T173">
+        <v>1.61</v>
+      </c>
+      <c r="U173">
+        <v>2.21</v>
+      </c>
+      <c r="V173">
+        <v>3.48</v>
+      </c>
+      <c r="W173">
+        <v>1.28</v>
+      </c>
+      <c r="X173">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y173">
+        <v>1.05</v>
+      </c>
+      <c r="Z173">
+        <v>2.7</v>
+      </c>
+      <c r="AA173">
+        <v>2.65</v>
+      </c>
+      <c r="AB173">
+        <v>3</v>
+      </c>
+      <c r="AC173">
+        <v>1.1</v>
+      </c>
+      <c r="AD173">
+        <v>5.2</v>
+      </c>
+      <c r="AE173">
+        <v>1.53</v>
+      </c>
+      <c r="AF173">
+        <v>2.45</v>
+      </c>
+      <c r="AG173">
+        <v>2.37</v>
+      </c>
+      <c r="AH173">
+        <v>1.51</v>
+      </c>
+      <c r="AI173">
+        <v>1.99</v>
+      </c>
+      <c r="AJ173">
+        <v>1.71</v>
+      </c>
+      <c r="AK173">
+        <v>1.37</v>
+      </c>
+      <c r="AL173">
+        <v>1.34</v>
+      </c>
+      <c r="AM173">
+        <v>1.42</v>
+      </c>
+      <c r="AN173">
+        <v>1.1</v>
+      </c>
+      <c r="AO173">
+        <v>1.3</v>
+      </c>
+      <c r="AP173">
+        <v>1.09</v>
+      </c>
+      <c r="AQ173">
+        <v>1.27</v>
+      </c>
+      <c r="AR173">
+        <v>1.4</v>
+      </c>
+      <c r="AS173">
+        <v>1.33</v>
+      </c>
+      <c r="AT173">
+        <v>2.73</v>
+      </c>
+      <c r="AU173">
+        <v>2</v>
+      </c>
+      <c r="AV173">
+        <v>2</v>
+      </c>
+      <c r="AW173">
+        <v>3</v>
+      </c>
+      <c r="AX173">
+        <v>12</v>
+      </c>
+      <c r="AY173">
+        <v>5</v>
+      </c>
+      <c r="AZ173">
+        <v>16</v>
+      </c>
+      <c r="BA173">
+        <v>2</v>
+      </c>
+      <c r="BB173">
+        <v>4</v>
+      </c>
+      <c r="BC173">
+        <v>6</v>
+      </c>
+      <c r="BD173">
+        <v>1.57</v>
+      </c>
+      <c r="BE173">
+        <v>6.75</v>
+      </c>
+      <c r="BF173">
+        <v>2.65</v>
+      </c>
+      <c r="BG173">
+        <v>1.34</v>
+      </c>
+      <c r="BH173">
+        <v>2.9</v>
+      </c>
+      <c r="BI173">
+        <v>1.58</v>
+      </c>
+      <c r="BJ173">
+        <v>2.18</v>
+      </c>
+      <c r="BK173">
+        <v>1.94</v>
+      </c>
+      <c r="BL173">
+        <v>1.73</v>
+      </c>
+      <c r="BM173">
+        <v>2.48</v>
+      </c>
+      <c r="BN173">
+        <v>1.45</v>
+      </c>
+      <c r="BO173">
+        <v>3.2</v>
+      </c>
+      <c r="BP173">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="277">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -601,6 +601,9 @@
     <t>['84', '90+1']</t>
   </si>
   <si>
+    <t>['84']</t>
+  </si>
+  <si>
     <t>['19']</t>
   </si>
   <si>
@@ -794,9 +797,6 @@
   </si>
   <si>
     <t>['90']</t>
-  </si>
-  <si>
-    <t>['84']</t>
   </si>
   <si>
     <t>['68', '82']</t>
@@ -1206,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1462,7 +1462,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -2286,7 +2286,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q6">
         <v>2.25</v>
@@ -2492,7 +2492,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2573,7 +2573,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ7">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2698,7 +2698,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2776,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ8">
         <v>1.18</v>
@@ -3316,7 +3316,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3522,7 +3522,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3728,7 +3728,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3809,7 +3809,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ13">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3934,7 +3934,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4140,7 +4140,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4346,7 +4346,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4758,7 +4758,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4964,7 +4964,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5170,7 +5170,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5457,7 +5457,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR21">
         <v>1.66</v>
@@ -5582,7 +5582,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5788,7 +5788,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ29">
         <v>1.27</v>
@@ -7230,7 +7230,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7436,7 +7436,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7642,7 +7642,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7848,7 +7848,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8054,7 +8054,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8260,7 +8260,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8466,7 +8466,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -8672,7 +8672,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9290,7 +9290,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9371,7 +9371,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9496,7 +9496,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9702,7 +9702,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -9780,7 +9780,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ42">
         <v>0.45</v>
@@ -9986,7 +9986,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -10401,7 +10401,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR45">
         <v>1.51</v>
@@ -10732,7 +10732,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11144,7 +11144,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12174,7 +12174,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12380,7 +12380,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12792,7 +12792,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13076,7 +13076,7 @@
         <v>1.25</v>
       </c>
       <c r="AP58">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ58">
         <v>1.09</v>
@@ -13204,7 +13204,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13282,7 +13282,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ59">
         <v>1.27</v>
@@ -13410,7 +13410,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13491,7 +13491,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ60">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR60">
         <v>1.71</v>
@@ -13822,7 +13822,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14109,7 +14109,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14852,7 +14852,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15264,7 +15264,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15470,7 +15470,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15676,7 +15676,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15882,7 +15882,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -15960,7 +15960,7 @@
         <v>0.8</v>
       </c>
       <c r="AP72">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ72">
         <v>0.45</v>
@@ -16169,7 +16169,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ73">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16375,7 +16375,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ74">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR74">
         <v>1.37</v>
@@ -16500,7 +16500,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16706,7 +16706,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16912,7 +16912,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17324,7 +17324,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17736,7 +17736,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18148,7 +18148,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18766,7 +18766,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19050,7 +19050,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ87">
         <v>1.18</v>
@@ -19465,7 +19465,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ89">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR89">
         <v>1.6</v>
@@ -19590,7 +19590,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19796,7 +19796,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20002,7 +20002,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20208,7 +20208,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20492,7 +20492,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ94">
         <v>1.09</v>
@@ -20620,7 +20620,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21525,7 +21525,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ99">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR99">
         <v>1.24</v>
@@ -21728,7 +21728,7 @@
         <v>0.67</v>
       </c>
       <c r="AP100">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ100">
         <v>0.55</v>
@@ -21856,7 +21856,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22474,7 +22474,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23092,7 +23092,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23173,7 +23173,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ107">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR107">
         <v>1.21</v>
@@ -23298,7 +23298,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23710,7 +23710,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23788,7 +23788,7 @@
         <v>1.63</v>
       </c>
       <c r="AP110">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ110">
         <v>1.55</v>
@@ -23916,7 +23916,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24122,7 +24122,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24203,7 +24203,7 @@
         <v>1</v>
       </c>
       <c r="AQ112">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24328,7 +24328,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24740,7 +24740,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25152,7 +25152,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25230,7 +25230,7 @@
         <v>1.6</v>
       </c>
       <c r="AP117">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ117">
         <v>1.73</v>
@@ -25976,7 +25976,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26057,7 +26057,7 @@
         <v>2</v>
       </c>
       <c r="AQ121">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR121">
         <v>1.14</v>
@@ -26182,7 +26182,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26466,7 +26466,7 @@
         <v>0.14</v>
       </c>
       <c r="AP123">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ123">
         <v>0.73</v>
@@ -26800,7 +26800,7 @@
         <v>86</v>
       </c>
       <c r="P125" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q125">
         <v>3.3</v>
@@ -27006,7 +27006,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27499,7 +27499,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ128">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR128">
         <v>1.38</v>
@@ -27702,7 +27702,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ129">
         <v>1.73</v>
@@ -28036,7 +28036,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28242,7 +28242,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28448,7 +28448,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28941,7 +28941,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ135">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR135">
         <v>1.36</v>
@@ -29066,7 +29066,7 @@
         <v>99</v>
       </c>
       <c r="P136" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Q136">
         <v>3.4</v>
@@ -29144,7 +29144,7 @@
         <v>0.57</v>
       </c>
       <c r="AP136">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ136">
         <v>0.5</v>
@@ -29556,7 +29556,7 @@
         <v>0.88</v>
       </c>
       <c r="AP138">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ138">
         <v>0.91</v>
@@ -30508,7 +30508,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30586,10 +30586,10 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ143">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR143">
         <v>1.8</v>
@@ -30714,7 +30714,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -31413,7 +31413,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR147">
         <v>1.41</v>
@@ -31538,7 +31538,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -32649,7 +32649,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ153">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR153">
         <v>1.53</v>
@@ -32852,7 +32852,7 @@
         <v>0.44</v>
       </c>
       <c r="AP154">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ154">
         <v>0.73</v>
@@ -33470,7 +33470,7 @@
         <v>1.33</v>
       </c>
       <c r="AP157">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ157">
         <v>1.09</v>
@@ -33885,7 +33885,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ159">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AR159">
         <v>1.46</v>
@@ -36276,7 +36276,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36845,6 +36845,418 @@
       </c>
       <c r="BP173">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7486984</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45676.54166666666</v>
+      </c>
+      <c r="F174">
+        <v>22</v>
+      </c>
+      <c r="G174" t="s">
+        <v>76</v>
+      </c>
+      <c r="H174" t="s">
+        <v>75</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>1</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>2</v>
+      </c>
+      <c r="O174" t="s">
+        <v>195</v>
+      </c>
+      <c r="P174" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q174">
+        <v>4.7</v>
+      </c>
+      <c r="R174">
+        <v>2.1</v>
+      </c>
+      <c r="S174">
+        <v>2.4</v>
+      </c>
+      <c r="T174">
+        <v>1.47</v>
+      </c>
+      <c r="U174">
+        <v>2.5</v>
+      </c>
+      <c r="V174">
+        <v>3.1</v>
+      </c>
+      <c r="W174">
+        <v>1.34</v>
+      </c>
+      <c r="X174">
+        <v>8.1</v>
+      </c>
+      <c r="Y174">
+        <v>1.06</v>
+      </c>
+      <c r="Z174">
+        <v>3.8</v>
+      </c>
+      <c r="AA174">
+        <v>3.2</v>
+      </c>
+      <c r="AB174">
+        <v>2</v>
+      </c>
+      <c r="AC174">
+        <v>1.05</v>
+      </c>
+      <c r="AD174">
+        <v>8</v>
+      </c>
+      <c r="AE174">
+        <v>1.35</v>
+      </c>
+      <c r="AF174">
+        <v>3.05</v>
+      </c>
+      <c r="AG174">
+        <v>2</v>
+      </c>
+      <c r="AH174">
+        <v>1.78</v>
+      </c>
+      <c r="AI174">
+        <v>1.87</v>
+      </c>
+      <c r="AJ174">
+        <v>1.8</v>
+      </c>
+      <c r="AK174">
+        <v>1.77</v>
+      </c>
+      <c r="AL174">
+        <v>1.27</v>
+      </c>
+      <c r="AM174">
+        <v>1.2</v>
+      </c>
+      <c r="AN174">
+        <v>1.2</v>
+      </c>
+      <c r="AO174">
+        <v>1.7</v>
+      </c>
+      <c r="AP174">
+        <v>1.18</v>
+      </c>
+      <c r="AQ174">
+        <v>1.64</v>
+      </c>
+      <c r="AR174">
+        <v>1.61</v>
+      </c>
+      <c r="AS174">
+        <v>1.25</v>
+      </c>
+      <c r="AT174">
+        <v>2.86</v>
+      </c>
+      <c r="AU174">
+        <v>8</v>
+      </c>
+      <c r="AV174">
+        <v>5</v>
+      </c>
+      <c r="AW174">
+        <v>16</v>
+      </c>
+      <c r="AX174">
+        <v>10</v>
+      </c>
+      <c r="AY174">
+        <v>27</v>
+      </c>
+      <c r="AZ174">
+        <v>19</v>
+      </c>
+      <c r="BA174">
+        <v>8</v>
+      </c>
+      <c r="BB174">
+        <v>7</v>
+      </c>
+      <c r="BC174">
+        <v>15</v>
+      </c>
+      <c r="BD174">
+        <v>2.4</v>
+      </c>
+      <c r="BE174">
+        <v>6.75</v>
+      </c>
+      <c r="BF174">
+        <v>1.7</v>
+      </c>
+      <c r="BG174">
+        <v>1.29</v>
+      </c>
+      <c r="BH174">
+        <v>3.15</v>
+      </c>
+      <c r="BI174">
+        <v>1.49</v>
+      </c>
+      <c r="BJ174">
+        <v>2.35</v>
+      </c>
+      <c r="BK174">
+        <v>1.81</v>
+      </c>
+      <c r="BL174">
+        <v>1.85</v>
+      </c>
+      <c r="BM174">
+        <v>2.25</v>
+      </c>
+      <c r="BN174">
+        <v>1.55</v>
+      </c>
+      <c r="BO174">
+        <v>2.88</v>
+      </c>
+      <c r="BP174">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7486667</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45676.64583333334</v>
+      </c>
+      <c r="F175">
+        <v>22</v>
+      </c>
+      <c r="G175" t="s">
+        <v>80</v>
+      </c>
+      <c r="H175" t="s">
+        <v>83</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>1</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>188</v>
+      </c>
+      <c r="P175" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q175">
+        <v>2.3</v>
+      </c>
+      <c r="R175">
+        <v>2.16</v>
+      </c>
+      <c r="S175">
+        <v>4.9</v>
+      </c>
+      <c r="T175">
+        <v>1.44</v>
+      </c>
+      <c r="U175">
+        <v>2.6</v>
+      </c>
+      <c r="V175">
+        <v>2.78</v>
+      </c>
+      <c r="W175">
+        <v>1.41</v>
+      </c>
+      <c r="X175">
+        <v>7</v>
+      </c>
+      <c r="Y175">
+        <v>1.08</v>
+      </c>
+      <c r="Z175">
+        <v>1.95</v>
+      </c>
+      <c r="AA175">
+        <v>3.4</v>
+      </c>
+      <c r="AB175">
+        <v>3.8</v>
+      </c>
+      <c r="AC175">
+        <v>1.03</v>
+      </c>
+      <c r="AD175">
+        <v>9</v>
+      </c>
+      <c r="AE175">
+        <v>1.29</v>
+      </c>
+      <c r="AF175">
+        <v>3.35</v>
+      </c>
+      <c r="AG175">
+        <v>1.97</v>
+      </c>
+      <c r="AH175">
+        <v>1.85</v>
+      </c>
+      <c r="AI175">
+        <v>1.79</v>
+      </c>
+      <c r="AJ175">
+        <v>1.87</v>
+      </c>
+      <c r="AK175">
+        <v>1.18</v>
+      </c>
+      <c r="AL175">
+        <v>1.24</v>
+      </c>
+      <c r="AM175">
+        <v>1.88</v>
+      </c>
+      <c r="AN175">
+        <v>1.9</v>
+      </c>
+      <c r="AO175">
+        <v>1.4</v>
+      </c>
+      <c r="AP175">
+        <v>1.82</v>
+      </c>
+      <c r="AQ175">
+        <v>1.36</v>
+      </c>
+      <c r="AR175">
+        <v>1.78</v>
+      </c>
+      <c r="AS175">
+        <v>1.16</v>
+      </c>
+      <c r="AT175">
+        <v>2.94</v>
+      </c>
+      <c r="AU175">
+        <v>8</v>
+      </c>
+      <c r="AV175">
+        <v>2</v>
+      </c>
+      <c r="AW175">
+        <v>6</v>
+      </c>
+      <c r="AX175">
+        <v>6</v>
+      </c>
+      <c r="AY175">
+        <v>15</v>
+      </c>
+      <c r="AZ175">
+        <v>9</v>
+      </c>
+      <c r="BA175">
+        <v>3</v>
+      </c>
+      <c r="BB175">
+        <v>3</v>
+      </c>
+      <c r="BC175">
+        <v>6</v>
+      </c>
+      <c r="BD175">
+        <v>1.27</v>
+      </c>
+      <c r="BE175">
+        <v>7.5</v>
+      </c>
+      <c r="BF175">
+        <v>4.1</v>
+      </c>
+      <c r="BG175">
+        <v>1.28</v>
+      </c>
+      <c r="BH175">
+        <v>3.2</v>
+      </c>
+      <c r="BI175">
+        <v>1.49</v>
+      </c>
+      <c r="BJ175">
+        <v>2.38</v>
+      </c>
+      <c r="BK175">
+        <v>1.78</v>
+      </c>
+      <c r="BL175">
+        <v>1.89</v>
+      </c>
+      <c r="BM175">
+        <v>2.2</v>
+      </c>
+      <c r="BN175">
+        <v>1.57</v>
+      </c>
+      <c r="BO175">
+        <v>2.8</v>
+      </c>
+      <c r="BP175">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="278">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -602,6 +602,9 @@
   </si>
   <si>
     <t>['84']</t>
+  </si>
+  <si>
+    <t>['20', '40']</t>
   </si>
   <si>
     <t>['19']</t>
@@ -1206,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1462,7 +1465,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1540,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ2">
         <v>1.18</v>
@@ -1955,7 +1958,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2286,7 +2289,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q6">
         <v>2.25</v>
@@ -2492,7 +2495,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2698,7 +2701,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3316,7 +3319,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3522,7 +3525,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3728,7 +3731,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3806,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ13">
         <v>1.64</v>
@@ -3934,7 +3937,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4140,7 +4143,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4346,7 +4349,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4758,7 +4761,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4964,7 +4967,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5170,7 +5173,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5582,7 +5585,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5660,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ22">
         <v>0.55</v>
@@ -5788,7 +5791,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6896,10 +6899,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR28">
         <v>1.74</v>
@@ -7230,7 +7233,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7436,7 +7439,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7642,7 +7645,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7720,7 +7723,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ32">
         <v>1.09</v>
@@ -7848,7 +7851,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8054,7 +8057,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8260,7 +8263,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8466,7 +8469,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -8672,7 +8675,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -9290,7 +9293,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9496,7 +9499,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9702,7 +9705,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10195,7 +10198,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR44">
         <v>2.23</v>
@@ -10398,7 +10401,7 @@
         <v>0.67</v>
       </c>
       <c r="AP45">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ45">
         <v>1.36</v>
@@ -10732,7 +10735,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -10810,7 +10813,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ47">
         <v>0.73</v>
@@ -11144,7 +11147,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -12174,7 +12177,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12380,7 +12383,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12792,7 +12795,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -12873,7 +12876,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR57">
         <v>1.23</v>
@@ -13204,7 +13207,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13410,7 +13413,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13488,7 +13491,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ60">
         <v>1.64</v>
@@ -13822,7 +13825,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14852,7 +14855,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15264,7 +15267,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15470,7 +15473,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15676,7 +15679,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15754,7 +15757,7 @@
         <v>1.8</v>
       </c>
       <c r="AP71">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ71">
         <v>1.55</v>
@@ -15882,7 +15885,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16500,7 +16503,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16706,7 +16709,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16784,7 +16787,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ76">
         <v>1.09</v>
@@ -16912,7 +16915,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17199,7 +17202,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17324,7 +17327,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17736,7 +17739,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18148,7 +18151,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18432,7 +18435,7 @@
         <v>1.8</v>
       </c>
       <c r="AP84">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ84">
         <v>1.18</v>
@@ -18766,7 +18769,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19462,7 +19465,7 @@
         <v>0.67</v>
       </c>
       <c r="AP89">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ89">
         <v>1.36</v>
@@ -19590,7 +19593,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19796,7 +19799,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -19877,7 +19880,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ91">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR91">
         <v>1.87</v>
@@ -20002,7 +20005,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20208,7 +20211,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20620,7 +20623,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -21856,7 +21859,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -22346,7 +22349,7 @@
         <v>0.6</v>
       </c>
       <c r="AP103">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ103">
         <v>0.91</v>
@@ -22474,7 +22477,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -22967,7 +22970,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR106">
         <v>1.16</v>
@@ -23092,7 +23095,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23298,7 +23301,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23710,7 +23713,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23916,7 +23919,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -23994,7 +23997,7 @@
         <v>1.29</v>
       </c>
       <c r="AP111">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ111">
         <v>1.45</v>
@@ -24122,7 +24125,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24328,7 +24331,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24740,7 +24743,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25152,7 +25155,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25642,7 +25645,7 @@
         <v>0.17</v>
       </c>
       <c r="AP119">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ119">
         <v>0.73</v>
@@ -25976,7 +25979,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26182,7 +26185,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26672,7 +26675,7 @@
         <v>0.86</v>
       </c>
       <c r="AP124">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26800,7 +26803,7 @@
         <v>86</v>
       </c>
       <c r="P125" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q125">
         <v>3.3</v>
@@ -27006,7 +27009,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -28036,7 +28039,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28114,7 +28117,7 @@
         <v>1.25</v>
       </c>
       <c r="AP131">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ131">
         <v>1.18</v>
@@ -28242,7 +28245,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28448,7 +28451,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -29147,7 +29150,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ136">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR136">
         <v>1.72</v>
@@ -29272,7 +29275,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29762,7 +29765,7 @@
         <v>1.5</v>
       </c>
       <c r="AP139">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ139">
         <v>1.27</v>
@@ -29890,7 +29893,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30177,7 +30180,7 @@
         <v>1</v>
       </c>
       <c r="AQ141">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR141">
         <v>1.41</v>
@@ -30302,7 +30305,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30508,7 +30511,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30714,7 +30717,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30920,7 +30923,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31332,7 +31335,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31538,7 +31541,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31744,7 +31747,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31950,7 +31953,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32568,7 +32571,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32774,7 +32777,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33061,7 +33064,7 @@
         <v>2</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR155">
         <v>1.16</v>
@@ -33392,7 +33395,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33598,7 +33601,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -34088,7 +34091,7 @@
         <v>1.67</v>
       </c>
       <c r="AP160">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ160">
         <v>1.73</v>
@@ -34294,7 +34297,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP161">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AQ161">
         <v>0.45</v>
@@ -34834,7 +34837,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -35246,7 +35249,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35864,7 +35867,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36070,7 +36073,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36276,7 +36279,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36482,7 +36485,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36894,7 +36897,7 @@
         <v>195</v>
       </c>
       <c r="P174" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q174">
         <v>4.7</v>
@@ -37257,6 +37260,418 @@
       </c>
       <c r="BP175">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7486666</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45677.5</v>
+      </c>
+      <c r="F176">
+        <v>22</v>
+      </c>
+      <c r="G176" t="s">
+        <v>70</v>
+      </c>
+      <c r="H176" t="s">
+        <v>73</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>1</v>
+      </c>
+      <c r="N176">
+        <v>2</v>
+      </c>
+      <c r="O176" t="s">
+        <v>113</v>
+      </c>
+      <c r="P176" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q176">
+        <v>2.6</v>
+      </c>
+      <c r="R176">
+        <v>2.08</v>
+      </c>
+      <c r="S176">
+        <v>4.1</v>
+      </c>
+      <c r="T176">
+        <v>1.48</v>
+      </c>
+      <c r="U176">
+        <v>2.5</v>
+      </c>
+      <c r="V176">
+        <v>2.99</v>
+      </c>
+      <c r="W176">
+        <v>1.36</v>
+      </c>
+      <c r="X176">
+        <v>8.1</v>
+      </c>
+      <c r="Y176">
+        <v>1.06</v>
+      </c>
+      <c r="Z176">
+        <v>2.05</v>
+      </c>
+      <c r="AA176">
+        <v>3.25</v>
+      </c>
+      <c r="AB176">
+        <v>3.4</v>
+      </c>
+      <c r="AC176">
+        <v>1.01</v>
+      </c>
+      <c r="AD176">
+        <v>8.6</v>
+      </c>
+      <c r="AE176">
+        <v>1.34</v>
+      </c>
+      <c r="AF176">
+        <v>3.05</v>
+      </c>
+      <c r="AG176">
+        <v>1.95</v>
+      </c>
+      <c r="AH176">
+        <v>1.75</v>
+      </c>
+      <c r="AI176">
+        <v>1.8</v>
+      </c>
+      <c r="AJ176">
+        <v>1.87</v>
+      </c>
+      <c r="AK176">
+        <v>1.26</v>
+      </c>
+      <c r="AL176">
+        <v>1.3</v>
+      </c>
+      <c r="AM176">
+        <v>1.62</v>
+      </c>
+      <c r="AN176">
+        <v>1.4</v>
+      </c>
+      <c r="AO176">
+        <v>1</v>
+      </c>
+      <c r="AP176">
+        <v>1.36</v>
+      </c>
+      <c r="AQ176">
+        <v>1</v>
+      </c>
+      <c r="AR176">
+        <v>1.54</v>
+      </c>
+      <c r="AS176">
+        <v>1.23</v>
+      </c>
+      <c r="AT176">
+        <v>2.77</v>
+      </c>
+      <c r="AU176">
+        <v>11</v>
+      </c>
+      <c r="AV176">
+        <v>4</v>
+      </c>
+      <c r="AW176">
+        <v>22</v>
+      </c>
+      <c r="AX176">
+        <v>3</v>
+      </c>
+      <c r="AY176">
+        <v>43</v>
+      </c>
+      <c r="AZ176">
+        <v>8</v>
+      </c>
+      <c r="BA176">
+        <v>12</v>
+      </c>
+      <c r="BB176">
+        <v>3</v>
+      </c>
+      <c r="BC176">
+        <v>15</v>
+      </c>
+      <c r="BD176">
+        <v>1.42</v>
+      </c>
+      <c r="BE176">
+        <v>7</v>
+      </c>
+      <c r="BF176">
+        <v>3.2</v>
+      </c>
+      <c r="BG176">
+        <v>1.22</v>
+      </c>
+      <c r="BH176">
+        <v>3.65</v>
+      </c>
+      <c r="BI176">
+        <v>1.4</v>
+      </c>
+      <c r="BJ176">
+        <v>2.65</v>
+      </c>
+      <c r="BK176">
+        <v>1.62</v>
+      </c>
+      <c r="BL176">
+        <v>2.1</v>
+      </c>
+      <c r="BM176">
+        <v>1.98</v>
+      </c>
+      <c r="BN176">
+        <v>1.7</v>
+      </c>
+      <c r="BO176">
+        <v>2.5</v>
+      </c>
+      <c r="BP176">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7486669</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45677.625</v>
+      </c>
+      <c r="F177">
+        <v>22</v>
+      </c>
+      <c r="G177" t="s">
+        <v>81</v>
+      </c>
+      <c r="H177" t="s">
+        <v>78</v>
+      </c>
+      <c r="I177">
+        <v>2</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>3</v>
+      </c>
+      <c r="L177">
+        <v>2</v>
+      </c>
+      <c r="M177">
+        <v>1</v>
+      </c>
+      <c r="N177">
+        <v>3</v>
+      </c>
+      <c r="O177" t="s">
+        <v>196</v>
+      </c>
+      <c r="P177" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q177">
+        <v>2.14</v>
+      </c>
+      <c r="R177">
+        <v>2.15</v>
+      </c>
+      <c r="S177">
+        <v>6</v>
+      </c>
+      <c r="T177">
+        <v>1.47</v>
+      </c>
+      <c r="U177">
+        <v>2.5</v>
+      </c>
+      <c r="V177">
+        <v>2.94</v>
+      </c>
+      <c r="W177">
+        <v>1.37</v>
+      </c>
+      <c r="X177">
+        <v>7.6</v>
+      </c>
+      <c r="Y177">
+        <v>1.07</v>
+      </c>
+      <c r="Z177">
+        <v>1.53</v>
+      </c>
+      <c r="AA177">
+        <v>3.9</v>
+      </c>
+      <c r="AB177">
+        <v>5.8</v>
+      </c>
+      <c r="AC177">
+        <v>1.05</v>
+      </c>
+      <c r="AD177">
+        <v>7.8</v>
+      </c>
+      <c r="AE177">
+        <v>1.34</v>
+      </c>
+      <c r="AF177">
+        <v>3.1</v>
+      </c>
+      <c r="AG177">
+        <v>2</v>
+      </c>
+      <c r="AH177">
+        <v>1.78</v>
+      </c>
+      <c r="AI177">
+        <v>2.02</v>
+      </c>
+      <c r="AJ177">
+        <v>1.68</v>
+      </c>
+      <c r="AK177">
+        <v>1.12</v>
+      </c>
+      <c r="AL177">
+        <v>1.22</v>
+      </c>
+      <c r="AM177">
+        <v>2.11</v>
+      </c>
+      <c r="AN177">
+        <v>1.7</v>
+      </c>
+      <c r="AO177">
+        <v>0.5</v>
+      </c>
+      <c r="AP177">
+        <v>1.82</v>
+      </c>
+      <c r="AQ177">
+        <v>0.45</v>
+      </c>
+      <c r="AR177">
+        <v>1.54</v>
+      </c>
+      <c r="AS177">
+        <v>1.35</v>
+      </c>
+      <c r="AT177">
+        <v>2.89</v>
+      </c>
+      <c r="AU177">
+        <v>8</v>
+      </c>
+      <c r="AV177">
+        <v>4</v>
+      </c>
+      <c r="AW177">
+        <v>13</v>
+      </c>
+      <c r="AX177">
+        <v>11</v>
+      </c>
+      <c r="AY177">
+        <v>25</v>
+      </c>
+      <c r="AZ177">
+        <v>17</v>
+      </c>
+      <c r="BA177">
+        <v>10</v>
+      </c>
+      <c r="BB177">
+        <v>4</v>
+      </c>
+      <c r="BC177">
+        <v>14</v>
+      </c>
+      <c r="BD177">
+        <v>1.46</v>
+      </c>
+      <c r="BE177">
+        <v>6.4</v>
+      </c>
+      <c r="BF177">
+        <v>3.15</v>
+      </c>
+      <c r="BG177">
+        <v>1.44</v>
+      </c>
+      <c r="BH177">
+        <v>2.5</v>
+      </c>
+      <c r="BI177">
+        <v>1.76</v>
+      </c>
+      <c r="BJ177">
+        <v>1.92</v>
+      </c>
+      <c r="BK177">
+        <v>2.2</v>
+      </c>
+      <c r="BL177">
+        <v>1.56</v>
+      </c>
+      <c r="BM177">
+        <v>2.9</v>
+      </c>
+      <c r="BN177">
+        <v>1.34</v>
+      </c>
+      <c r="BO177">
+        <v>3.9</v>
+      </c>
+      <c r="BP177">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Romania Liga I_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="279">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>['20', '40']</t>
+  </si>
+  <si>
+    <t>['57', '75', '87']</t>
   </si>
   <si>
     <t>['19']</t>
@@ -1209,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP177"/>
+  <dimension ref="A1:BP179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1465,7 +1468,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1546,7 +1549,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ2">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2289,7 +2292,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q6">
         <v>2.25</v>
@@ -2370,7 +2373,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ6">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2495,7 +2498,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2701,7 +2704,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -3319,7 +3322,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q11">
         <v>5.5</v>
@@ -3525,7 +3528,7 @@
         <v>94</v>
       </c>
       <c r="P12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
@@ -3731,7 +3734,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q13">
         <v>3.44</v>
@@ -3937,7 +3940,7 @@
         <v>96</v>
       </c>
       <c r="P14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q14">
         <v>2.88</v>
@@ -4143,7 +4146,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q15">
         <v>2.88</v>
@@ -4221,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ15">
         <v>1.27</v>
@@ -4349,7 +4352,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q16">
         <v>4.33</v>
@@ -4427,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ16">
         <v>1.09</v>
@@ -4761,7 +4764,7 @@
         <v>92</v>
       </c>
       <c r="P18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
@@ -4842,7 +4845,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ18">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR18">
         <v>0.84</v>
@@ -4967,7 +4970,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q19">
         <v>2</v>
@@ -5173,7 +5176,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -5585,7 +5588,7 @@
         <v>86</v>
       </c>
       <c r="P22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
@@ -5791,7 +5794,7 @@
         <v>86</v>
       </c>
       <c r="P23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q23">
         <v>2.35</v>
@@ -6078,7 +6081,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ24">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
         <v>1.56</v>
@@ -6693,7 +6696,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ27">
         <v>0.45</v>
@@ -7233,7 +7236,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q30">
         <v>2.77</v>
@@ -7314,7 +7317,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ30">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.69</v>
@@ -7439,7 +7442,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -7645,7 +7648,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q32">
         <v>2.61</v>
@@ -7851,7 +7854,7 @@
         <v>105</v>
       </c>
       <c r="P33" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8057,7 +8060,7 @@
         <v>106</v>
       </c>
       <c r="P34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q34">
         <v>2.8</v>
@@ -8263,7 +8266,7 @@
         <v>107</v>
       </c>
       <c r="P35" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8469,7 +8472,7 @@
         <v>108</v>
       </c>
       <c r="P36" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q36">
         <v>4</v>
@@ -8547,7 +8550,7 @@
         <v>0.5</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ36">
         <v>1.09</v>
@@ -8675,7 +8678,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>2.95</v>
@@ -8962,7 +8965,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ38">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR38">
         <v>1.73</v>
@@ -9168,7 +9171,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ39">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR39">
         <v>0.8100000000000001</v>
@@ -9293,7 +9296,7 @@
         <v>111</v>
       </c>
       <c r="P40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q40">
         <v>3.3</v>
@@ -9499,7 +9502,7 @@
         <v>99</v>
       </c>
       <c r="P41" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q41">
         <v>3.15</v>
@@ -9705,7 +9708,7 @@
         <v>112</v>
       </c>
       <c r="P42" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
@@ -10735,7 +10738,7 @@
         <v>116</v>
       </c>
       <c r="P47" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -11147,7 +11150,7 @@
         <v>117</v>
       </c>
       <c r="P49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q49">
         <v>3.65</v>
@@ -11434,7 +11437,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ50">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR50">
         <v>1.71</v>
@@ -11637,7 +11640,7 @@
         <v>2.33</v>
       </c>
       <c r="AP51">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ51">
         <v>1.45</v>
@@ -12177,7 +12180,7 @@
         <v>86</v>
       </c>
       <c r="P54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q54">
         <v>4.3</v>
@@ -12255,10 +12258,10 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ54">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR54">
         <v>1.5</v>
@@ -12383,7 +12386,7 @@
         <v>121</v>
       </c>
       <c r="P55" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q55">
         <v>3.6</v>
@@ -12795,7 +12798,7 @@
         <v>123</v>
       </c>
       <c r="P57" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q57">
         <v>2.75</v>
@@ -13207,7 +13210,7 @@
         <v>86</v>
       </c>
       <c r="P59" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q59">
         <v>3.51</v>
@@ -13413,7 +13416,7 @@
         <v>86</v>
       </c>
       <c r="P60" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q60">
         <v>3.3</v>
@@ -13825,7 +13828,7 @@
         <v>126</v>
       </c>
       <c r="P62" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q62">
         <v>2.88</v>
@@ -14521,10 +14524,10 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ65">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR65">
         <v>1.18</v>
@@ -14727,7 +14730,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ66">
         <v>1.18</v>
@@ -14855,7 +14858,7 @@
         <v>130</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q67">
         <v>3.6</v>
@@ -15267,7 +15270,7 @@
         <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q69">
         <v>2.91</v>
@@ -15473,7 +15476,7 @@
         <v>133</v>
       </c>
       <c r="P70" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q70">
         <v>2.99</v>
@@ -15679,7 +15682,7 @@
         <v>86</v>
       </c>
       <c r="P71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q71">
         <v>2.55</v>
@@ -15760,7 +15763,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ71">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.35</v>
@@ -15885,7 +15888,7 @@
         <v>134</v>
       </c>
       <c r="P72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16503,7 +16506,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75">
         <v>2.05</v>
@@ -16709,7 +16712,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16915,7 +16918,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17327,7 +17330,7 @@
         <v>100</v>
       </c>
       <c r="P79" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q79">
         <v>4.68</v>
@@ -17739,7 +17742,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17817,7 +17820,7 @@
         <v>0.6</v>
       </c>
       <c r="AP81">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ81">
         <v>0.55</v>
@@ -18026,7 +18029,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ82">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
         <v>1.61</v>
@@ -18151,7 +18154,7 @@
         <v>141</v>
       </c>
       <c r="P83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q83">
         <v>1.95</v>
@@ -18641,7 +18644,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ85">
         <v>0.91</v>
@@ -18769,7 +18772,7 @@
         <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
@@ -19056,7 +19059,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ87">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR87">
         <v>1.94</v>
@@ -19593,7 +19596,7 @@
         <v>145</v>
       </c>
       <c r="P90" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q90">
         <v>4.5</v>
@@ -19674,7 +19677,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ90">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -19799,7 +19802,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q91">
         <v>1.95</v>
@@ -20005,7 +20008,7 @@
         <v>147</v>
       </c>
       <c r="P92" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q92">
         <v>3.6</v>
@@ -20211,7 +20214,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q93">
         <v>3.34</v>
@@ -20623,7 +20626,7 @@
         <v>149</v>
       </c>
       <c r="P95" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q95">
         <v>1.73</v>
@@ -20907,7 +20910,7 @@
         <v>0.2</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ96">
         <v>0.73</v>
@@ -21859,7 +21862,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q101">
         <v>4.5</v>
@@ -21937,7 +21940,7 @@
         <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ101">
         <v>1.73</v>
@@ -22146,7 +22149,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ102">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR102">
         <v>1.5</v>
@@ -22477,7 +22480,7 @@
         <v>155</v>
       </c>
       <c r="P104" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q104">
         <v>2.4</v>
@@ -23095,7 +23098,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23301,7 +23304,7 @@
         <v>86</v>
       </c>
       <c r="P108" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q108">
         <v>2.63</v>
@@ -23382,7 +23385,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ108">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR108">
         <v>1.42</v>
@@ -23713,7 +23716,7 @@
         <v>158</v>
       </c>
       <c r="P110" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23794,7 +23797,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ110">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR110">
         <v>1.9</v>
@@ -23919,7 +23922,7 @@
         <v>159</v>
       </c>
       <c r="P111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q111">
         <v>3.65</v>
@@ -24125,7 +24128,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q112">
         <v>5.5</v>
@@ -24203,7 +24206,7 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ112">
         <v>1.64</v>
@@ -24331,7 +24334,7 @@
         <v>160</v>
       </c>
       <c r="P113" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24615,7 +24618,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ114">
         <v>1</v>
@@ -24743,7 +24746,7 @@
         <v>162</v>
       </c>
       <c r="P115" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q115">
         <v>3.6</v>
@@ -25155,7 +25158,7 @@
         <v>127</v>
       </c>
       <c r="P117" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q117">
         <v>2.88</v>
@@ -25979,7 +25982,7 @@
         <v>124</v>
       </c>
       <c r="P121" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q121">
         <v>3.68</v>
@@ -26057,7 +26060,7 @@
         <v>1.8</v>
       </c>
       <c r="AP121">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ121">
         <v>1.64</v>
@@ -26185,7 +26188,7 @@
         <v>165</v>
       </c>
       <c r="P122" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q122">
         <v>3.72</v>
@@ -26803,7 +26806,7 @@
         <v>86</v>
       </c>
       <c r="P125" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q125">
         <v>3.3</v>
@@ -27009,7 +27012,7 @@
         <v>168</v>
       </c>
       <c r="P126" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q126">
         <v>3.52</v>
@@ -27293,7 +27296,7 @@
         <v>1.29</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ127">
         <v>1.27</v>
@@ -28039,7 +28042,7 @@
         <v>86</v>
       </c>
       <c r="P131" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q131">
         <v>3.2</v>
@@ -28245,7 +28248,7 @@
         <v>171</v>
       </c>
       <c r="P132" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q132">
         <v>4.33</v>
@@ -28326,7 +28329,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ132">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR132">
         <v>1.25</v>
@@ -28451,7 +28454,7 @@
         <v>172</v>
       </c>
       <c r="P133" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q133">
         <v>2.88</v>
@@ -28738,7 +28741,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ134">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR134">
         <v>2.06</v>
@@ -29275,7 +29278,7 @@
         <v>174</v>
       </c>
       <c r="P137" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q137">
         <v>4.33</v>
@@ -29893,7 +29896,7 @@
         <v>176</v>
       </c>
       <c r="P140" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q140">
         <v>3.5</v>
@@ -30177,7 +30180,7 @@
         <v>0.63</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ141">
         <v>0.45</v>
@@ -30305,7 +30308,7 @@
         <v>137</v>
       </c>
       <c r="P142" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q142">
         <v>3</v>
@@ -30383,7 +30386,7 @@
         <v>1.38</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ142">
         <v>1.09</v>
@@ -30511,7 +30514,7 @@
         <v>86</v>
       </c>
       <c r="P143" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q143">
         <v>3.15</v>
@@ -30717,7 +30720,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q144">
         <v>2.38</v>
@@ -30923,7 +30926,7 @@
         <v>175</v>
       </c>
       <c r="P145" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q145">
         <v>4.75</v>
@@ -31335,7 +31338,7 @@
         <v>86</v>
       </c>
       <c r="P147" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q147">
         <v>4</v>
@@ -31413,7 +31416,7 @@
         <v>1.22</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ147">
         <v>1.36</v>
@@ -31541,7 +31544,7 @@
         <v>179</v>
       </c>
       <c r="P148" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31747,7 +31750,7 @@
         <v>180</v>
       </c>
       <c r="P149" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q149">
         <v>2.75</v>
@@ -31828,7 +31831,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ149">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR149">
         <v>1.6</v>
@@ -31953,7 +31956,7 @@
         <v>181</v>
       </c>
       <c r="P150" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q150">
         <v>3</v>
@@ -32571,7 +32574,7 @@
         <v>183</v>
       </c>
       <c r="P153" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q153">
         <v>3.6</v>
@@ -32777,7 +32780,7 @@
         <v>184</v>
       </c>
       <c r="P154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q154">
         <v>3.25</v>
@@ -33061,7 +33064,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ155">
         <v>0.45</v>
@@ -33395,7 +33398,7 @@
         <v>186</v>
       </c>
       <c r="P157" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q157">
         <v>2.5</v>
@@ -33601,7 +33604,7 @@
         <v>187</v>
       </c>
       <c r="P158" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q158">
         <v>2.63</v>
@@ -34506,7 +34509,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ162">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR162">
         <v>1.45</v>
@@ -34837,7 +34840,7 @@
         <v>86</v>
       </c>
       <c r="P164" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q164">
         <v>5</v>
@@ -34915,7 +34918,7 @@
         <v>1.3</v>
       </c>
       <c r="AP164">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ164">
         <v>1.45</v>
@@ -35124,7 +35127,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ165">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR165">
         <v>1.27</v>
@@ -35249,7 +35252,7 @@
         <v>191</v>
       </c>
       <c r="P166" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q166">
         <v>2.4</v>
@@ -35533,7 +35536,7 @@
         <v>1.1</v>
       </c>
       <c r="AP167">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ167">
         <v>1.09</v>
@@ -35867,7 +35870,7 @@
         <v>86</v>
       </c>
       <c r="P169" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q169">
         <v>5.5</v>
@@ -36073,7 +36076,7 @@
         <v>193</v>
       </c>
       <c r="P170" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q170">
         <v>3.9</v>
@@ -36279,7 +36282,7 @@
         <v>98</v>
       </c>
       <c r="P171" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q171">
         <v>1.99</v>
@@ -36485,7 +36488,7 @@
         <v>194</v>
       </c>
       <c r="P172" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q172">
         <v>2.14</v>
@@ -36897,7 +36900,7 @@
         <v>195</v>
       </c>
       <c r="P174" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q174">
         <v>4.7</v>
@@ -37515,7 +37518,7 @@
         <v>196</v>
       </c>
       <c r="P177" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q177">
         <v>2.14</v>
@@ -37672,6 +37675,418 @@
       </c>
       <c r="BP177">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7486985</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45681.5</v>
+      </c>
+      <c r="F178">
+        <v>23</v>
+      </c>
+      <c r="G178" t="s">
+        <v>84</v>
+      </c>
+      <c r="H178" t="s">
+        <v>79</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>3</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>3</v>
+      </c>
+      <c r="O178" t="s">
+        <v>197</v>
+      </c>
+      <c r="P178" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q178">
+        <v>3.15</v>
+      </c>
+      <c r="R178">
+        <v>1.93</v>
+      </c>
+      <c r="S178">
+        <v>3.7</v>
+      </c>
+      <c r="T178">
+        <v>1.58</v>
+      </c>
+      <c r="U178">
+        <v>2.25</v>
+      </c>
+      <c r="V178">
+        <v>3.44</v>
+      </c>
+      <c r="W178">
+        <v>1.28</v>
+      </c>
+      <c r="X178">
+        <v>9.4</v>
+      </c>
+      <c r="Y178">
+        <v>1.04</v>
+      </c>
+      <c r="Z178">
+        <v>2.48</v>
+      </c>
+      <c r="AA178">
+        <v>3.02</v>
+      </c>
+      <c r="AB178">
+        <v>2.98</v>
+      </c>
+      <c r="AC178">
+        <v>1.07</v>
+      </c>
+      <c r="AD178">
+        <v>7</v>
+      </c>
+      <c r="AE178">
+        <v>1.46</v>
+      </c>
+      <c r="AF178">
+        <v>2.6</v>
+      </c>
+      <c r="AG178">
+        <v>2.4</v>
+      </c>
+      <c r="AH178">
+        <v>1.5</v>
+      </c>
+      <c r="AI178">
+        <v>1.97</v>
+      </c>
+      <c r="AJ178">
+        <v>1.72</v>
+      </c>
+      <c r="AK178">
+        <v>1.35</v>
+      </c>
+      <c r="AL178">
+        <v>1.33</v>
+      </c>
+      <c r="AM178">
+        <v>1.45</v>
+      </c>
+      <c r="AN178">
+        <v>1</v>
+      </c>
+      <c r="AO178">
+        <v>1.18</v>
+      </c>
+      <c r="AP178">
+        <v>1.17</v>
+      </c>
+      <c r="AQ178">
+        <v>1.08</v>
+      </c>
+      <c r="AR178">
+        <v>1.45</v>
+      </c>
+      <c r="AS178">
+        <v>1.28</v>
+      </c>
+      <c r="AT178">
+        <v>2.73</v>
+      </c>
+      <c r="AU178">
+        <v>6</v>
+      </c>
+      <c r="AV178">
+        <v>6</v>
+      </c>
+      <c r="AW178">
+        <v>6</v>
+      </c>
+      <c r="AX178">
+        <v>4</v>
+      </c>
+      <c r="AY178">
+        <v>13</v>
+      </c>
+      <c r="AZ178">
+        <v>11</v>
+      </c>
+      <c r="BA178">
+        <v>4</v>
+      </c>
+      <c r="BB178">
+        <v>5</v>
+      </c>
+      <c r="BC178">
+        <v>9</v>
+      </c>
+      <c r="BD178">
+        <v>1.52</v>
+      </c>
+      <c r="BE178">
+        <v>6.75</v>
+      </c>
+      <c r="BF178">
+        <v>3.34</v>
+      </c>
+      <c r="BG178">
+        <v>1.31</v>
+      </c>
+      <c r="BH178">
+        <v>2.92</v>
+      </c>
+      <c r="BI178">
+        <v>1.59</v>
+      </c>
+      <c r="BJ178">
+        <v>2.16</v>
+      </c>
+      <c r="BK178">
+        <v>2.03</v>
+      </c>
+      <c r="BL178">
+        <v>1.7</v>
+      </c>
+      <c r="BM178">
+        <v>2.67</v>
+      </c>
+      <c r="BN178">
+        <v>1.39</v>
+      </c>
+      <c r="BO178">
+        <v>3.58</v>
+      </c>
+      <c r="BP178">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7486673</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45681.625</v>
+      </c>
+      <c r="F179">
+        <v>23</v>
+      </c>
+      <c r="G179" t="s">
+        <v>83</v>
+      </c>
+      <c r="H179" t="s">
+        <v>82</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179" t="s">
+        <v>86</v>
+      </c>
+      <c r="P179" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q179">
+        <v>3.2</v>
+      </c>
+      <c r="R179">
+        <v>1.97</v>
+      </c>
+      <c r="S179">
+        <v>3.45</v>
+      </c>
+      <c r="T179">
+        <v>1.55</v>
+      </c>
+      <c r="U179">
+        <v>2.32</v>
+      </c>
+      <c r="V179">
+        <v>3.28</v>
+      </c>
+      <c r="W179">
+        <v>1.31</v>
+      </c>
+      <c r="X179">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y179">
+        <v>1.05</v>
+      </c>
+      <c r="Z179">
+        <v>2.58</v>
+      </c>
+      <c r="AA179">
+        <v>3.15</v>
+      </c>
+      <c r="AB179">
+        <v>2.75</v>
+      </c>
+      <c r="AC179">
+        <v>1.06</v>
+      </c>
+      <c r="AD179">
+        <v>7.5</v>
+      </c>
+      <c r="AE179">
+        <v>1.5</v>
+      </c>
+      <c r="AF179">
+        <v>2.4</v>
+      </c>
+      <c r="AG179">
+        <v>2.47</v>
+      </c>
+      <c r="AH179">
+        <v>1.48</v>
+      </c>
+      <c r="AI179">
+        <v>1.88</v>
+      </c>
+      <c r="AJ179">
+        <v>1.8</v>
+      </c>
+      <c r="AK179">
+        <v>1.39</v>
+      </c>
+      <c r="AL179">
+        <v>1.31</v>
+      </c>
+      <c r="AM179">
+        <v>1.43</v>
+      </c>
+      <c r="AN179">
+        <v>2</v>
+      </c>
+      <c r="AO179">
+        <v>1.55</v>
+      </c>
+      <c r="AP179">
+        <v>1.92</v>
+      </c>
+      <c r="AQ179">
+        <v>1.5</v>
+      </c>
+      <c r="AR179">
+        <v>1.24</v>
+      </c>
+      <c r="AS179">
+        <v>1.37</v>
+      </c>
+      <c r="AT179">
+        <v>2.61</v>
+      </c>
+      <c r="AU179">
+        <v>4</v>
+      </c>
+      <c r="AV179">
+        <v>2</v>
+      </c>
+      <c r="AW179">
+        <v>6</v>
+      </c>
+      <c r="AX179">
+        <v>14</v>
+      </c>
+      <c r="AY179">
+        <v>12</v>
+      </c>
+      <c r="AZ179">
+        <v>21</v>
+      </c>
+      <c r="BA179">
+        <v>4</v>
+      </c>
+      <c r="BB179">
+        <v>4</v>
+      </c>
+      <c r="BC179">
+        <v>8</v>
+      </c>
+      <c r="BD179">
+        <v>2.24</v>
+      </c>
+      <c r="BE179">
+        <v>6.2</v>
+      </c>
+      <c r="BF179">
+        <v>2.01</v>
+      </c>
+      <c r="BG179">
+        <v>1.35</v>
+      </c>
+      <c r="BH179">
+        <v>2.74</v>
+      </c>
+      <c r="BI179">
+        <v>1.66</v>
+      </c>
+      <c r="BJ179">
+        <v>2.04</v>
+      </c>
+      <c r="BK179">
+        <v>2.14</v>
+      </c>
+      <c r="BL179">
+        <v>1.63</v>
+      </c>
+      <c r="BM179">
+        <v>2.84</v>
+      </c>
+      <c r="BN179">
+        <v>1.35</v>
+      </c>
+      <c r="BO179">
+        <v>3.96</v>
+      </c>
+      <c r="BP179">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
